--- a/Referenztabelle_Rechnungen.xlsx
+++ b/Referenztabelle_Rechnungen.xlsx
@@ -1,20 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fgroup-my.sharepoint.com/personal/leonard_verclas_freudenberg_com/Documents/02_Studium_DHBW/PA 2/Projektarbeit_2/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_1373589E6EA26D9A1A97E98B862CC5E341F0CACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{197868DF-8A72-4890-813F-A7FED2AE9AAB}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rechnungsuebersicht" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Rechnungsuebersicht" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Rechnungsuebersicht!$A$1:$O$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Rechnungsuebersicht!$A$1:$O$101</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,12 +39,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="N7" authorId="0">
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -36,7 +52,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fälligkeit betrifft nur den Restbetrag - 50 % waren bereits als Anzahlung fällig.</t>
+          <t>Fälligkeit betrifft nur den Restbetrag - 50 % waren bereits als Anzahlung fällig.</t>
         </r>
       </text>
     </comment>
@@ -47,2642 +63,2640 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="875">
   <si>
-    <t xml:space="preserve">Kundenname (Leistungsempfaenger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechnungsnummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechnungsdatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leistungszeitraum / -datum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kundennummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referenz-Art</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referenznummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lieferant / Rechnungssteller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leistungsbeschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nettobetrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steuersatz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USt-Betrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechnungsbetrag (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faelligkeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dateiname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg &amp; Co. Kommanditgesellschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE-2026-047382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.08.2026 - 31.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KD-100248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bestellnummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-FBG-2026-3391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordlicht IT Solutions GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Copilot Premium Abonnement (Softwarelizenzen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_Rechnung_Copilot.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-B-14872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.02.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K-40182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lieferschein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LS-2026-0912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontorwerk Bürobedarf GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Büromaterial und Druckerzubehör</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02_Rechnung_Bueromaterial.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg IT SE &amp; Co. KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE-2026-0221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.05.2026 - 31.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-2210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projekt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S/4HANA Rollout Phase 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kestner Consulting GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT-Beratung (S/4HANA Rollout Phase 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_RechnungIT_Beratung.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg Sealing Technologies GmbH &amp; Co. KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WA-26-00745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.04.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftragsnummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Südwest Klimatechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wartung Klima- und Lüftungstechnik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04_Rechnung_Wartung_Klimatechnik.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg Filtration Technologies SE &amp; Co. KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SP-2026-118934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.06.2026 - 26.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sendungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Aufträge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rheinlogistik Spedition GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frachtkosten Spedition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05_Rechnung_Spedition.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg Home and Cleaning Solutions GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/MB/0417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.05.2026 - 15.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HM-1188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veranstaltung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFAT München 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hellwig Messe &amp; Event GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messestand und Werbemittel (IFAT München 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_Rechnung_Messebau.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEM-2026-0093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.02.2026 - 11.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN-3307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buchungsnummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B-2026-0451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akademie Neckartal GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schulung und Weiterbildung (Inhouse-Seminar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07_Rechnung_Weiterbildung.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg Performance Materials Holding SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-2026-55218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.07.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-11884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bergmann Technischer Handel GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industriebedarf und Normteile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08_Rechnung.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GR-2026-0431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.03.2026 - 31.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KW-2044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RV-2024-77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klarwerk Gebäudedienste GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gebäudereinigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09_Rechnung_Gebaeudereinigung.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RG-2026-3387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.01.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC-6621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angebot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN-2025-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datacore Systemhaus AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netzwerkhardware und Installation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10_Rechnung_Netzwerktechnik.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZA-2026-2205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.07.2026 - 02.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP-1140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Überlassung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KW 30 und 31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odenwald Personalservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personaldienstleistung (Zeitarbeit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11_Rechnung_Zeitarbeit.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-2026-884102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.01.2026 - 31.01.2026 (Abrechnungszeitraum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V-880412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zählernummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1EMH0071842366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhein-Neckar Energie AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stromlieferung Werk 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12_Rechnung_Stromlieferung_SR-2026-884102.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG-26-004417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.02.2026 - 28.02.2026 (Abrechnungszeitraum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertragskonto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VK-4471209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terragas Versorgung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erdgaslieferung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13_Rechnung_Erdgaslieferung_TG-26-004417.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KT-2026-77219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9911472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rahmenvertrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RV-MOB-2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konnex Telekom GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telekommunikation Mobilfunk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14_Rechnung_Telekommunikation_KT-2026-77219.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CU-2026-0318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KUN-3312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BK-2023-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Culina Betriebsgastronomie GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kantinenbewirtschaftung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15_Rechnung_Kantinenbewirtschaftung_CU-2026-0318.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WF-26-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-10442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werkfein Präzisionstechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lohnfertigung Drehteile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16_Rechnung_Lohnfertigung_WF-26-1180.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freudenberg Medical Europe GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ML-2026-0642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.04.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-26-3391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metrolab Kalibrierservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalibrierung Messmittel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17_Rechnung_Kalibrierung_ML-2026-0642.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE-26-5518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.04.2026 - 30.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-7702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entsorgungsnachweis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EN-2026-0117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reko Entsorgung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abfallentsorgung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18_Rechnung_Abfallentsorgung_RE-26-5518.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-2026-0904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-4021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MS-2022-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Textilis Berufskleidung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berufskleidung Mietservice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19_Rechnung_Berufskleidung_TX-2026-0904.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AF-2026-11204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.06.2026 - 30.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FP-2210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LV-2025-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autoflott Leasing GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuhrpark Leasingraten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20_Rechnung_Fuhrpark_AF-2026-11204.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HO-2026-2288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.06.2026 - 10.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-1140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reservierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RES-88214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bergstraße Tagungshotel GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tagung und Übernachtungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21_Rechnung_Tagung_HO-2026-2288.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LX-2026-0331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.04.2026 - 30.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M-2026-114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mandat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lieferantenrahmenverträge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lexara Rechtsanwälte PartG mbB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rechtsberatung Vertragsrecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22_Rechnung_Rechtsberatung_LX-2026-0331.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KWP-2026-0088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.01.2026 - 06.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WP-0042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auftrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JA-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konsul Wirtschaftsprüfung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahresabschlussprüfung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23_Rechnung_Jahresabschlusspruefung_KWP-2026-0088.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-26-0417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.05.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aktenzeichen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DE 10 2026 004 118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patentis Patentanwälte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patentanmeldung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24_Rechnung_Patentanmeldung_PA-26-0417.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LU-2026-1442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.04.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-8802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Betriebsanleitung Vliesanlage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lingua Fachübersetzungen GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fachübersetzungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25_Rechnung_Fachuebersetzungen_LU-2026-1442.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OD-2026-3390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.05.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-5511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AU-26-8841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Offset Druck Rhein-Main GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katalogdruck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26_Rechnung_Katalogdruck_OD-2026-3390.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PW-2026-0221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.03.2026 - 26.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX-3040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relaunch Markenauftritt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixelwerk Digitalagentur GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website-Relaunch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27_Rechnung_Website-Relaunch_PW-2026-0221.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS-2026-0771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.02.2026 - 31.01.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS-1024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN-2025-9912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADsoft Vertriebs GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAD-Softwarelizenzen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28_Rechnung_CAD-Softwarelizenzen_CS-2026-0771.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NC-2026-08841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NC-7781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA-2024-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordcloud Hosting GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud-Hosting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29_Rechnung_Cloud-Hosting_NC-2026-08841.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SK-2026-0455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.02.2026 - 28.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SK-9012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS-2023-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sekurit Werkschutz GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werkschutz und Pforte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30_Rechnung_Werkschutz_SK-2026-0455.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HT-26-2214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H-3388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mietvertrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MV-2025-41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hebetec Flurförderzeuge GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staplermiete und Wartung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31_Rechnung_Staplermiete_HT-26-2214.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX-2026-6612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.05.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-12204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palux Verpackungen GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportverpackungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32_Rechnung_Transportverpackungen_PX-2026-6612.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CL-2026-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.02.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CL-6620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-09117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemlab Laborbedarf GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laborbedarf und Chemikalien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33_Rechnung_Laborbedarf_CL-2026-4471.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP-2026-0993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.06.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MA-4410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prüfbericht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB-2026-0771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materia Prüflabor GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materialprüfung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34_Rechnung_Materialpruefung_MP-2026-0993.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ-2026-0208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.03.2026 - 25.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ-1177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zertifikat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISO 9001:2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certum Zertifizierung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISO-Zertifizierungsaudit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35_Rechnung_ISO-Zertifizierungsaudit_CZ-2026-0208.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VA-2026-0771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VA-2288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wartungsvertrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WV-2021-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertikal Aufzugservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufzugswartung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36_Rechnung_Aufzugswartung_VA-2026-0771.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VE-2026-1188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.05.2026 - 20.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VM-1409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltmann Elektrotechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektroinstallation Halle D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37_Rechnung_Elektroinstallation_VE-2026-1188.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FW-26-0339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.06.2026 - 14.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FW-880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-26-1102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farbwerk Malerbetrieb GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malerarbeiten Verwaltungsgebäude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38_Rechnung_Malerarbeiten_FW-26-0339.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GW-2026-0512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.07.2026 - 31.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GW-2255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pflegevertrag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PV-2024-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grünwerk Gartenpflege GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pflege der Außenanlagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39_Rechnung_Pflege_GW-2026-0512.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WD-2026-0044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.01.2026 - 31.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WF-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WD-2025-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winterfest Dienstleistungen GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winterdienst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40_Rechnung_Winterdienst_WD-2026-0044.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST-2026-7719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.06.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-11907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensotec Messtechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messtechnik Ersatzteile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41_Rechnung_Messtechnik_ST-2026-7719.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HF-26-3308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-12771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydroflex Schlauchtechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydraulikschläuche und Armaturen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42_Rechnung_Hydraulikschlaeuche_HF-26-3308.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SK-2026-88117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.02.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-09884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stahlkontor Südwest GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stahlblech Rohmaterial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43_Rechnung_Stahlblech_SK-2026-88117.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM-2026-5504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.03.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-10118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polymera Kunststoffhandel GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kunststoffgranulat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44_Rechnung_Kunststoffgranulat_PM-2026-5504.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS-2026-0117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.01.2026 - 31.12.2026 (Versicherungsperiode)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AS-3311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policennummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TV-2026-448120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assekur Industriemakler GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportversicherung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45_Rechnung_Transportversicherung_AS-2026-0117.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA-2026-0662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.06.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TA-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vakanz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leitung IT-Infrastruktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talentis Personalberatung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personalvermittlung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46_Rechnung_Personalvermittlung_TA-2026-0662.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EF-2026-2201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.04.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EF-4402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-10662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ergoform Büroeinrichtung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Büromöbel und Ergonomie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47_Rechnung_Bueromoebel_EF-2026-2201.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQ-2026-1104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQ-7714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SV-2023-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aquavit Wasserspender GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserspender und Kaffeeservice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48_Rechnung_Wasserspender_AQ-2026-1104.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VS-2026-0388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.02.2026 - 24.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VS-2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kursnummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE-2026-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verbal Sprachinstitut GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprachkurse Business English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49_Rechnung_Sprachkurse_VS-2026-0388.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B8-2026-0227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.07.2026 - 17.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B8-1150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagefilm Nachhaltigkeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blende8 Film und Foto GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagefilm und Fotoproduktion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50_Rechnung_Imagefilm_B8-2026-0227.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FV-2026-0912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AB-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abonummer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-99120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fachpresse Verlag GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fachliteratur und Abonnements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51_Rechnung_Fachliteratur_FV-2026-0912.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR-2026-3341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.02.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM-2208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-09441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promota Werbemittel GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werbeartikel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52_Rechnung_Werbeartikel_PR-2026-3341.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KE-2026-11408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KE-3312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sammelabrechnung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-2026-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurierexpress Rhein-Neckar GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurierfahrten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53_Rechnung_Kurierfahrten_KE-2026-11408.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD-2026-0448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV-2024-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sekurdoc Aktenservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aktenvernichtung und Archivierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54_Rechnung_Aktenvernichtung_SD-2026-0448.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IK-2026-0217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.04.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IK-2044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesellschafterversammlung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interlingua Konferenzdienst GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dolmetscherdienst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55_Rechnung_Dolmetscherdienst_IK-2026-0217.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SA-2026-0331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.01.2026 - 31.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI-7702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASiG-2024-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicura Arbeitsschutz Beratung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbeitssicherheit Betreuung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56_Rechnung_Arbeitssicherheit_SA-2026-0331.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS-2026-1104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.05.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PY-4402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pyrostop Brandschutztechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandschutzwartung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57_Rechnung_Brandschutzwartung_PS-2026-1104.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LW-2026-0662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.06.2026 - 31.05.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LW-3390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-2026-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lernwerk Digital GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-Learning Unterweisungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58_Rechnung_E-Learning_LW-2026-0662.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT-2026-0774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.06.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT-1150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-26-2214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtec Drucklufttechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Druckluftanlagen Wartung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59_Rechnung_Druckluftanlagen_AT-2026-0774.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WP-2026-8814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-12008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weldpro Schweißtechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schweißzusatzwerkstoffe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60_Rechnung_Schweisszusatzwerkstoffe_WP-2026-8814.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO-2026-2219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.07.2026 - 24.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT-6620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-12441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coatec Oberflächentechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lohnbeschichtung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.08.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61_Rechnung_Lohnbeschichtung_CO-2026-2219.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TH-2026-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.07.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-3308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-12660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thermica Härterei GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wärmebehandlung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62_Rechnung_Waermebehandlung_TH-2026-4471.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT-2026-7719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.08.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-12881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuttec Zerspanungswerkzeuge GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zerspanungswerkzeuge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63_Rechnung_Zerspanungswerkzeuge_CT-2026-7719.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LM-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LX-2255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FM-2025-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lubrimax Fluidservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kühlschmierstoffmanagement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64_Rechnung_Kuehlschmierstoffmanagement_LM-2026-0338.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX-2026-0114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.08.2026 - 05.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB-1188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handlingzelle Linie 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robotix Automation GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roboterintegration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65_Rechnung_Roboterintegration_RX-2026-0114.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-2026-0552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.09.2026 - 18.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SL-4409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steuerlogik Systemtechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPS-Programmierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66_Rechnung_SPS-Programmierung_SL-2026-0552.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT-2026-6640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.09.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-13114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pumptec Industrieservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pumpen Ersatzteile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67_Rechnung_Pumpen_PT-2026-6640.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LC-2026-0993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.09.2026 - 02.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LC-2044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB-2026-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liftcheck Prüfgesellschaft mbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kranprüfung UVV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68_Rechnung_Kranpruefung_LC-2026-0993.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RI-2026-0447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.10.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RI-3311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-1244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rackinspect Lagertechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regalinspektion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69_Rechnung_Regalinspektion_RI-2026-0447.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB-2026-1150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.09.2026 - 30.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB-8804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MV-2026-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modulbau Raumsysteme GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baucontainer Miete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70_Rechnung_Baucontainer_MB-2026-1150.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB-2026-0228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.09.2026 - 16.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BB-1102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Betonbau Südwest GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundamentarbeiten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71_Rechnung_Fundamentarbeiten_BB-2026-0228.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DW-2026-0771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.10.2026 - 28.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DW-2210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-1088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dachwerk Bedachungen GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dachsanierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72_Rechnung_Dachsanierung_DW-2026-0771.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.10.2026 - 06.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK-4402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-1177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glasklar Fensterbau GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fensterbau und Verglasung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73_Rechnung_Fensterbau_GK-2026-0338.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LW-2026-2204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.11.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LK-6612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-13440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lockwell Schließsysteme GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zutrittskontrolle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74_Rechnung_Zutrittskontrolle_LW-2026-2204.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT-2026-0885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.11.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VS-3390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-13511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visiotec Sicherheitstechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Videoueberwachung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75_Rechnung_Videoueberwachung_VT-2026-0885.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN-2026-4417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02.11.2026 - 25.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN-1204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standortanbindung Werk 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fibernet Infrastruktur GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glasfaseranschluss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76_Rechnung_Glasfaseranschluss_FN-2026-4417.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SX-2026-0662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03.12.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SX-8811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN-2026-0447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storix Datensysteme GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage-System</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77_Rechnung_Storage-System_SX-2026-0662.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-2026-11840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.11.2026 - 30.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EC-2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMS-2025-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERPcare Servicegesellschaft mbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP-Wartung und Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.01.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78_Rechnung_SAP-Wartung_EC-2026-11840.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DH-2026-0774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.01.2026 - 31.12.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AN-2025-8814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbankhaus Vertriebs GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datenbanklizenzen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79_Rechnung_Datenbanklizenzen_DH-2026-0774.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CB-2026-0117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.01.2026 - 23.01.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS-3302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pentest Produktionsnetz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybershield Security GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT-Security Penetrationstest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80_Rechnung_IT-Security_CB-2026-0117.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PF-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PF-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPS-2024-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printflow Bueroservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Managed Print Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81_Rechnung_Managed_PF-2026-0338.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VC-2026-2214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.02.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VC-7714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-09660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voicecom Kommunikationssysteme GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telefonanlage UCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82_Rechnung_Telefonanlage_VC-2026-2214.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MV-2026-0093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05.01.2026 - 13.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MV-2288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Studie Reinigungsmarkt EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markview Marktforschung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marktforschungsstudie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83_Rechnung_Marktforschungsstudie_MV-2026-0093.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG-2026-0441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.02.2026 - 20.02.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG-1104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portfolioanalyse 2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategika Unternehmensberatung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategieberatung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84_Rechnung_Strategieberatung_SG-2026-0441.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KP-2026-0662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.02.2026 - 01.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KP-3311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KW 08 und 09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontor Personalservice GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeitarbeit kaufmännisch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85_Rechnung_Zeitarbeit_KP-2026-0662.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UP-2026-0227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.02.2026 - 08.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UP-4409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umzugsprofis Rhein-Neckar GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Betriebsumzug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86_Rechnung_Betriebsumzug_UP-2026-0227.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HF-2026-0118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.02.2026 - 13.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HF-2201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holzform Objekttischlerei GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sondermöbelbau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87_Rechnung_Sondermoebelbau_HF-2026-0118.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG-2026-1180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.03.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST-5511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-2026-0551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signaltechnik Werbedesign GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beschilderung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88_Rechnung_Beschilderung_SG-2026-1180.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RL-2026-0552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.03.2026 - 27.03.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RL-1140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radiolab Prüftechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zerstörungsfreie Prüfung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89_Rechnung_Zerstoerungsfreie_RL-2026-0552.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CR-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.04.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CR-2255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RR-2024-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleanroom Systems GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reinraumwartung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90_Rechnung_Reinraumwartung_CR-2026-0338.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HL-2026-0771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.04.2026 - 10.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HL-3308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB-2026-0447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrolab Wasseranalytik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trinkwasseranalyse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91_Rechnung_Trinkwasseranalyse_HL-2026-0771.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VI-2026-0448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VI-1188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SB-2023-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitalis Schädlingsbekämpfung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schädlingsmonitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92_Rechnung_Schaedlingsmonitoring_VI-2026-0448.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RZ-2026-2204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.04.2026 - 24.04.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RZ-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL-2025-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reifenzentrum Südwest GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reifenservice Fuhrpark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93_Rechnung_Reifenservice_RZ-2026-2204.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TP-2026-88410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TP-1204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kartenkreis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-2026-114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tankpartner Kraftstoffe GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kraftstoff Tankkarten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94_Rechnung_Kraftstoff_TP-2026-88410.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FM-2026-1140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FX-2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MW-2025-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flexmobil Autovermietung GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mietwagen Langzeitmiete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95_Rechnung_Mietwagen_FM-2026-1140.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LP-2026-3390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.05.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-11220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labelpro Kennzeichnungstechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etiketten und Kennzeichnung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96_Rechnung_Etiketten_LP-2026-3390.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WB-2026-0338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WB-2255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WV-2024-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werksbus Verkehrsbetrieb GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werksbusverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97_Rechnung_Werksbusverkehr_WB-2026-0338.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FW-2026-0771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.05.2026 (Leistungsdatum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FE-3311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sommerfest 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Festwerk Eventagentur GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sommerfest Betriebsfeier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98_Rechnung_Sommerfest_FW-2026-0771.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KP-2026-4471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klimapartner Gerätetechnik GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klimageräte Beschaffung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99_Rechnung_Klimageraete_KP-2026-4471.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT-2026-5518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO-2026-11991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protega Arbeitsschutz GmbH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persönliche Schutzausrüstung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100_Rechnung_Persoenliche_PT-2026-5518.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legende:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaue Schrift = Wert aus der Original-Rechnung (Netto, Steuersatz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schwarze Schrift = berechnet (USt = Netto x Steuersatz, Brutto = Netto + USt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeilen 2-12: Rechnungen 01-11 | 13-51: Rechnungen 12-50 | 52-101: Rechnungen 51-100</t>
+    <t>Kundenname (Leistungsempfaenger)</t>
+  </si>
+  <si>
+    <t>Rechnungsnummer</t>
+  </si>
+  <si>
+    <t>Rechnungsdatum</t>
+  </si>
+  <si>
+    <t>Leistungszeitraum / -datum</t>
+  </si>
+  <si>
+    <t>Kundennummer</t>
+  </si>
+  <si>
+    <t>Referenz-Art</t>
+  </si>
+  <si>
+    <t>Referenznummer</t>
+  </si>
+  <si>
+    <t>Lieferant / Rechnungssteller</t>
+  </si>
+  <si>
+    <t>Leistungsbeschreibung</t>
+  </si>
+  <si>
+    <t>Nettobetrag</t>
+  </si>
+  <si>
+    <t>Steuersatz</t>
+  </si>
+  <si>
+    <t>USt-Betrag</t>
+  </si>
+  <si>
+    <t>Rechnungsbetrag (brutto)</t>
+  </si>
+  <si>
+    <t>Faelligkeit</t>
+  </si>
+  <si>
+    <t>Dateiname</t>
+  </si>
+  <si>
+    <t>Freudenberg &amp; Co. Kommanditgesellschaft</t>
+  </si>
+  <si>
+    <t>RE-2026-047382</t>
+  </si>
+  <si>
+    <t>14.08.2026</t>
+  </si>
+  <si>
+    <t>01.08.2026 - 31.08.2026</t>
+  </si>
+  <si>
+    <t>KD-100248</t>
+  </si>
+  <si>
+    <t>Bestellnummer</t>
+  </si>
+  <si>
+    <t>PO-FBG-2026-3391</t>
+  </si>
+  <si>
+    <t>Nordlicht IT Solutions GmbH</t>
+  </si>
+  <si>
+    <t>Microsoft Copilot Premium Abonnement (Softwarelizenzen)</t>
+  </si>
+  <si>
+    <t>28.08.2026</t>
+  </si>
+  <si>
+    <t>01_Rechnung_Copilot.pdf</t>
+  </si>
+  <si>
+    <t>2026-B-14872</t>
+  </si>
+  <si>
+    <t>03.03.2026</t>
+  </si>
+  <si>
+    <t>27.02.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>K-40182</t>
+  </si>
+  <si>
+    <t>Lieferschein</t>
+  </si>
+  <si>
+    <t>LS-2026-0912</t>
+  </si>
+  <si>
+    <t>Kontorwerk Bürobedarf GmbH</t>
+  </si>
+  <si>
+    <t>Büromaterial und Druckerzubehör</t>
+  </si>
+  <si>
+    <t>17.03.2026</t>
+  </si>
+  <si>
+    <t>02_Rechnung_Bueromaterial.pdf</t>
+  </si>
+  <si>
+    <t>Freudenberg IT SE &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>RE-2026-0221</t>
+  </si>
+  <si>
+    <t>31.05.2026</t>
+  </si>
+  <si>
+    <t>01.05.2026 - 31.05.2026</t>
+  </si>
+  <si>
+    <t>C-2210</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>S/4HANA Rollout Phase 2</t>
+  </si>
+  <si>
+    <t>Kestner Consulting GmbH</t>
+  </si>
+  <si>
+    <t>IT-Beratung (S/4HANA Rollout Phase 2)</t>
+  </si>
+  <si>
+    <t>30.06.2026</t>
+  </si>
+  <si>
+    <t>03_RechnungIT_Beratung.pdf</t>
+  </si>
+  <si>
+    <t>Freudenberg Sealing Technologies GmbH &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>WA-26-00745</t>
+  </si>
+  <si>
+    <t>12.04.2026</t>
+  </si>
+  <si>
+    <t>08.04.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>Auftragsnummer</t>
+  </si>
+  <si>
+    <t>A-2026-0331</t>
+  </si>
+  <si>
+    <t>Südwest Klimatechnik GmbH</t>
+  </si>
+  <si>
+    <t>Wartung Klima- und Lüftungstechnik</t>
+  </si>
+  <si>
+    <t>03.05.2026</t>
+  </si>
+  <si>
+    <t>04_Rechnung_Wartung_Klimatechnik.pdf</t>
+  </si>
+  <si>
+    <t>Freudenberg Filtration Technologies SE &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>SP-2026-118934</t>
+  </si>
+  <si>
+    <t>28.06.2026</t>
+  </si>
+  <si>
+    <t>15.06.2026 - 26.06.2026</t>
+  </si>
+  <si>
+    <t>70441</t>
+  </si>
+  <si>
+    <t>Sendungen</t>
+  </si>
+  <si>
+    <t>14 Aufträge</t>
+  </si>
+  <si>
+    <t>Rheinlogistik Spedition GmbH</t>
+  </si>
+  <si>
+    <t>Frachtkosten Spedition</t>
+  </si>
+  <si>
+    <t>12.07.2026</t>
+  </si>
+  <si>
+    <t>05_Rechnung_Spedition.pdf</t>
+  </si>
+  <si>
+    <t>Freudenberg Home and Cleaning Solutions GmbH</t>
+  </si>
+  <si>
+    <t>2026/MB/0417</t>
+  </si>
+  <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>11.05.2026 - 15.05.2026</t>
+  </si>
+  <si>
+    <t>HM-1188</t>
+  </si>
+  <si>
+    <t>Veranstaltung</t>
+  </si>
+  <si>
+    <t>IFAT München 2026</t>
+  </si>
+  <si>
+    <t>Hellwig Messe &amp; Event GmbH</t>
+  </si>
+  <si>
+    <t>Messestand und Werbemittel (IFAT München 2026)</t>
+  </si>
+  <si>
+    <t>12.06.2026</t>
+  </si>
+  <si>
+    <t>06_Rechnung_Messebau.pdf</t>
+  </si>
+  <si>
+    <t>SEM-2026-0093</t>
+  </si>
+  <si>
+    <t>17.02.2026</t>
+  </si>
+  <si>
+    <t>09.02.2026 - 11.02.2026</t>
+  </si>
+  <si>
+    <t>AN-3307</t>
+  </si>
+  <si>
+    <t>Buchungsnummer</t>
+  </si>
+  <si>
+    <t>B-2026-0451</t>
+  </si>
+  <si>
+    <t>Akademie Neckartal GmbH</t>
+  </si>
+  <si>
+    <t>Schulung und Weiterbildung (Inhouse-Seminar)</t>
+  </si>
+  <si>
+    <t>07_Rechnung_Weiterbildung.pdf</t>
+  </si>
+  <si>
+    <t>Freudenberg Performance Materials Holding SE</t>
+  </si>
+  <si>
+    <t>L-2026-55218</t>
+  </si>
+  <si>
+    <t>09.07.2026</t>
+  </si>
+  <si>
+    <t>07.07.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>50913</t>
+  </si>
+  <si>
+    <t>PO-2026-11884</t>
+  </si>
+  <si>
+    <t>Bergmann Technischer Handel GmbH</t>
+  </si>
+  <si>
+    <t>Industriebedarf und Normteile</t>
+  </si>
+  <si>
+    <t>23.07.2026</t>
+  </si>
+  <si>
+    <t>08_Rechnung.pdf</t>
+  </si>
+  <si>
+    <t>GR-2026-0431</t>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+  </si>
+  <si>
+    <t>01.03.2026 - 31.03.2026</t>
+  </si>
+  <si>
+    <t>KW-2044</t>
+  </si>
+  <si>
+    <t>Vertrag</t>
+  </si>
+  <si>
+    <t>RV-2024-77</t>
+  </si>
+  <si>
+    <t>Klarwerk Gebäudedienste GmbH</t>
+  </si>
+  <si>
+    <t>Gebäudereinigung</t>
+  </si>
+  <si>
+    <t>01.05.2026</t>
+  </si>
+  <si>
+    <t>09_Rechnung_Gebaeudereinigung.pdf</t>
+  </si>
+  <si>
+    <t>RG-2026-3387</t>
+  </si>
+  <si>
+    <t>19.01.2026</t>
+  </si>
+  <si>
+    <t>16.01.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>DC-6621</t>
+  </si>
+  <si>
+    <t>Angebot</t>
+  </si>
+  <si>
+    <t>AN-2025-4471</t>
+  </si>
+  <si>
+    <t>Datacore Systemhaus AG</t>
+  </si>
+  <si>
+    <t>Netzwerkhardware und Installation</t>
+  </si>
+  <si>
+    <t>08.02.2026</t>
+  </si>
+  <si>
+    <t>10_Rechnung_Netzwerktechnik.pdf</t>
+  </si>
+  <si>
+    <t>ZA-2026-2205</t>
+  </si>
+  <si>
+    <t>06.08.2026</t>
+  </si>
+  <si>
+    <t>20.07.2026 - 02.08.2026</t>
+  </si>
+  <si>
+    <t>OP-1140</t>
+  </si>
+  <si>
+    <t>Überlassung</t>
+  </si>
+  <si>
+    <t>KW 30 und 31</t>
+  </si>
+  <si>
+    <t>Odenwald Personalservice GmbH</t>
+  </si>
+  <si>
+    <t>Personaldienstleistung (Zeitarbeit)</t>
+  </si>
+  <si>
+    <t>16.08.2026</t>
+  </si>
+  <si>
+    <t>11_Rechnung_Zeitarbeit.pdf</t>
+  </si>
+  <si>
+    <t>SR-2026-884102</t>
+  </si>
+  <si>
+    <t>05.02.2026</t>
+  </si>
+  <si>
+    <t>01.01.2026 - 31.01.2026 (Abrechnungszeitraum)</t>
+  </si>
+  <si>
+    <t>V-880412</t>
+  </si>
+  <si>
+    <t>Zählernummer</t>
+  </si>
+  <si>
+    <t>1EMH0071842366</t>
+  </si>
+  <si>
+    <t>Rhein-Neckar Energie AG</t>
+  </si>
+  <si>
+    <t>Stromlieferung Werk 2</t>
+  </si>
+  <si>
+    <t>26.02.2026</t>
+  </si>
+  <si>
+    <t>12_Rechnung_Stromlieferung_SR-2026-884102.pdf</t>
+  </si>
+  <si>
+    <t>TG-26-004417</t>
+  </si>
+  <si>
+    <t>09.03.2026</t>
+  </si>
+  <si>
+    <t>01.02.2026 - 28.02.2026 (Abrechnungszeitraum)</t>
+  </si>
+  <si>
+    <t>80014</t>
+  </si>
+  <si>
+    <t>Vertragskonto</t>
+  </si>
+  <si>
+    <t>VK-4471209</t>
+  </si>
+  <si>
+    <t>Terragas Versorgung GmbH</t>
+  </si>
+  <si>
+    <t>Erdgaslieferung</t>
+  </si>
+  <si>
+    <t>23.03.2026</t>
+  </si>
+  <si>
+    <t>13_Rechnung_Erdgaslieferung_TG-26-004417.pdf</t>
+  </si>
+  <si>
+    <t>KT-2026-77219</t>
+  </si>
+  <si>
+    <t>9911472</t>
+  </si>
+  <si>
+    <t>Rahmenvertrag</t>
+  </si>
+  <si>
+    <t>RV-MOB-2024</t>
+  </si>
+  <si>
+    <t>Konnex Telekom GmbH</t>
+  </si>
+  <si>
+    <t>Telekommunikation Mobilfunk</t>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+  </si>
+  <si>
+    <t>14_Rechnung_Telekommunikation_KT-2026-77219.pdf</t>
+  </si>
+  <si>
+    <t>CU-2026-0318</t>
+  </si>
+  <si>
+    <t>02.04.2026</t>
+  </si>
+  <si>
+    <t>KUN-3312</t>
+  </si>
+  <si>
+    <t>BK-2023-09</t>
+  </si>
+  <si>
+    <t>Culina Betriebsgastronomie GmbH</t>
+  </si>
+  <si>
+    <t>Kantinenbewirtschaftung</t>
+  </si>
+  <si>
+    <t>02.05.2026</t>
+  </si>
+  <si>
+    <t>15_Rechnung_Kantinenbewirtschaftung_CU-2026-0318.pdf</t>
+  </si>
+  <si>
+    <t>WF-26-1180</t>
+  </si>
+  <si>
+    <t>16.03.2026</t>
+  </si>
+  <si>
+    <t>13.03.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>22014</t>
+  </si>
+  <si>
+    <t>PO-2026-10442</t>
+  </si>
+  <si>
+    <t>Werkfein Präzisionstechnik GmbH</t>
+  </si>
+  <si>
+    <t>Lohnfertigung Drehteile</t>
+  </si>
+  <si>
+    <t>16_Rechnung_Lohnfertigung_WF-26-1180.pdf</t>
+  </si>
+  <si>
+    <t>Freudenberg Medical Europe GmbH</t>
+  </si>
+  <si>
+    <t>ML-2026-0642</t>
+  </si>
+  <si>
+    <t>21.04.2026</t>
+  </si>
+  <si>
+    <t>17.04.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>MT-1180</t>
+  </si>
+  <si>
+    <t>A-26-3391</t>
+  </si>
+  <si>
+    <t>Metrolab Kalibrierservice GmbH</t>
+  </si>
+  <si>
+    <t>Kalibrierung Messmittel</t>
+  </si>
+  <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>17_Rechnung_Kalibrierung_ML-2026-0642.pdf</t>
+  </si>
+  <si>
+    <t>RE-26-5518</t>
+  </si>
+  <si>
+    <t>04.05.2026</t>
+  </si>
+  <si>
+    <t>01.04.2026 - 30.04.2026</t>
+  </si>
+  <si>
+    <t>E-7702</t>
+  </si>
+  <si>
+    <t>Entsorgungsnachweis</t>
+  </si>
+  <si>
+    <t>EN-2026-0117</t>
+  </si>
+  <si>
+    <t>Reko Entsorgung GmbH</t>
+  </si>
+  <si>
+    <t>Abfallentsorgung</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>18_Rechnung_Abfallentsorgung_RE-26-5518.pdf</t>
+  </si>
+  <si>
+    <t>TX-2026-0904</t>
+  </si>
+  <si>
+    <t>07.05.2026</t>
+  </si>
+  <si>
+    <t>T-4021</t>
+  </si>
+  <si>
+    <t>MS-2022-14</t>
+  </si>
+  <si>
+    <t>Textilis Berufskleidung GmbH</t>
+  </si>
+  <si>
+    <t>Berufskleidung Mietservice</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>19_Rechnung_Berufskleidung_TX-2026-0904.pdf</t>
+  </si>
+  <si>
+    <t>AF-2026-11204</t>
+  </si>
+  <si>
+    <t>01.06.2026</t>
+  </si>
+  <si>
+    <t>01.06.2026 - 30.06.2026</t>
+  </si>
+  <si>
+    <t>FP-2210</t>
+  </si>
+  <si>
+    <t>LV-2025-08</t>
+  </si>
+  <si>
+    <t>Autoflott Leasing GmbH</t>
+  </si>
+  <si>
+    <t>Fuhrpark Leasingraten</t>
+  </si>
+  <si>
+    <t>11.06.2026</t>
+  </si>
+  <si>
+    <t>20_Rechnung_Fuhrpark_AF-2026-11204.pdf</t>
+  </si>
+  <si>
+    <t>HO-2026-2288</t>
+  </si>
+  <si>
+    <t>08.06.2026 - 10.06.2026</t>
+  </si>
+  <si>
+    <t>G-1140</t>
+  </si>
+  <si>
+    <t>Reservierung</t>
+  </si>
+  <si>
+    <t>RES-88214</t>
+  </si>
+  <si>
+    <t>Bergstraße Tagungshotel GmbH</t>
+  </si>
+  <si>
+    <t>Tagung und Übernachtungen</t>
+  </si>
+  <si>
+    <t>26.06.2026</t>
+  </si>
+  <si>
+    <t>21_Rechnung_Tagung_HO-2026-2288.pdf</t>
+  </si>
+  <si>
+    <t>LX-2026-0331</t>
+  </si>
+  <si>
+    <t>01.04.2026 - 30.06.2026</t>
+  </si>
+  <si>
+    <t>M-2026-114</t>
+  </si>
+  <si>
+    <t>Mandat</t>
+  </si>
+  <si>
+    <t>Lieferantenrahmenverträge</t>
+  </si>
+  <si>
+    <t>Lexara Rechtsanwälte PartG mbB</t>
+  </si>
+  <si>
+    <t>Rechtsberatung Vertragsrecht</t>
+  </si>
+  <si>
+    <t>21.07.2026</t>
+  </si>
+  <si>
+    <t>22_Rechnung_Rechtsberatung_LX-2026-0331.pdf</t>
+  </si>
+  <si>
+    <t>KWP-2026-0088</t>
+  </si>
+  <si>
+    <t>20.03.2026</t>
+  </si>
+  <si>
+    <t>12.01.2026 - 06.03.2026</t>
+  </si>
+  <si>
+    <t>WP-0042</t>
+  </si>
+  <si>
+    <t>Auftrag</t>
+  </si>
+  <si>
+    <t>JA-2025</t>
+  </si>
+  <si>
+    <t>Konsul Wirtschaftsprüfung GmbH</t>
+  </si>
+  <si>
+    <t>Jahresabschlussprüfung</t>
+  </si>
+  <si>
+    <t>19.04.2026</t>
+  </si>
+  <si>
+    <t>23_Rechnung_Jahresabschlusspruefung_KWP-2026-0088.pdf</t>
+  </si>
+  <si>
+    <t>PA-26-0417</t>
+  </si>
+  <si>
+    <t>11.05.2026</t>
+  </si>
+  <si>
+    <t>06.05.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>P-2019</t>
+  </si>
+  <si>
+    <t>Aktenzeichen</t>
+  </si>
+  <si>
+    <t>DE 10 2026 004 118</t>
+  </si>
+  <si>
+    <t>Patentis Patentanwälte</t>
+  </si>
+  <si>
+    <t>Patentanmeldung</t>
+  </si>
+  <si>
+    <t>24_Rechnung_Patentanmeldung_PA-26-0417.pdf</t>
+  </si>
+  <si>
+    <t>LU-2026-1442</t>
+  </si>
+  <si>
+    <t>24.04.2026</t>
+  </si>
+  <si>
+    <t>22.04.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>L-8802</t>
+  </si>
+  <si>
+    <t>Betriebsanleitung Vliesanlage</t>
+  </si>
+  <si>
+    <t>Lingua Fachübersetzungen GmbH</t>
+  </si>
+  <si>
+    <t>Fachübersetzungen</t>
+  </si>
+  <si>
+    <t>08.05.2026</t>
+  </si>
+  <si>
+    <t>25_Rechnung_Fachuebersetzungen_LU-2026-1442.pdf</t>
+  </si>
+  <si>
+    <t>OD-2026-3390</t>
+  </si>
+  <si>
+    <t>15.05.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>D-5511</t>
+  </si>
+  <si>
+    <t>AU-26-8841</t>
+  </si>
+  <si>
+    <t>Offset Druck Rhein-Main GmbH</t>
+  </si>
+  <si>
+    <t>Katalogdruck</t>
+  </si>
+  <si>
+    <t>26_Rechnung_Katalogdruck_OD-2026-3390.pdf</t>
+  </si>
+  <si>
+    <t>PW-2026-0221</t>
+  </si>
+  <si>
+    <t>29.06.2026</t>
+  </si>
+  <si>
+    <t>02.03.2026 - 26.06.2026</t>
+  </si>
+  <si>
+    <t>PX-3040</t>
+  </si>
+  <si>
+    <t>Relaunch Markenauftritt</t>
+  </si>
+  <si>
+    <t>Pixelwerk Digitalagentur GmbH</t>
+  </si>
+  <si>
+    <t>Website-Relaunch</t>
+  </si>
+  <si>
+    <t>20.07.2026</t>
+  </si>
+  <si>
+    <t>27_Rechnung_Website-Relaunch_PW-2026-0221.pdf</t>
+  </si>
+  <si>
+    <t>CS-2026-0771</t>
+  </si>
+  <si>
+    <t>15.01.2026</t>
+  </si>
+  <si>
+    <t>01.02.2026 - 31.01.2027</t>
+  </si>
+  <si>
+    <t>CS-1024</t>
+  </si>
+  <si>
+    <t>AN-2025-9912</t>
+  </si>
+  <si>
+    <t>CADsoft Vertriebs GmbH</t>
+  </si>
+  <si>
+    <t>CAD-Softwarelizenzen</t>
+  </si>
+  <si>
+    <t>14.02.2026</t>
+  </si>
+  <si>
+    <t>28_Rechnung_CAD-Softwarelizenzen_CS-2026-0771.pdf</t>
+  </si>
+  <si>
+    <t>NC-2026-08841</t>
+  </si>
+  <si>
+    <t>01.07.2026</t>
+  </si>
+  <si>
+    <t>NC-7781</t>
+  </si>
+  <si>
+    <t>SLA-2024-06</t>
+  </si>
+  <si>
+    <t>Nordcloud Hosting GmbH</t>
+  </si>
+  <si>
+    <t>Cloud-Hosting</t>
+  </si>
+  <si>
+    <t>15.07.2026</t>
+  </si>
+  <si>
+    <t>29_Rechnung_Cloud-Hosting_NC-2026-08841.pdf</t>
+  </si>
+  <si>
+    <t>SK-2026-0455</t>
+  </si>
+  <si>
+    <t>01.02.2026 - 28.02.2026</t>
+  </si>
+  <si>
+    <t>SK-9012</t>
+  </si>
+  <si>
+    <t>WS-2023-11</t>
+  </si>
+  <si>
+    <t>Sekurit Werkschutz GmbH</t>
+  </si>
+  <si>
+    <t>Werkschutz und Pforte</t>
+  </si>
+  <si>
+    <t>24.03.2026</t>
+  </si>
+  <si>
+    <t>30_Rechnung_Werkschutz_SK-2026-0455.pdf</t>
+  </si>
+  <si>
+    <t>HT-26-2214</t>
+  </si>
+  <si>
+    <t>08.04.2026</t>
+  </si>
+  <si>
+    <t>H-3388</t>
+  </si>
+  <si>
+    <t>Mietvertrag</t>
+  </si>
+  <si>
+    <t>MV-2025-41</t>
+  </si>
+  <si>
+    <t>Hebetec Flurförderzeuge GmbH</t>
+  </si>
+  <si>
+    <t>Staplermiete und Wartung</t>
+  </si>
+  <si>
+    <t>29.04.2026</t>
+  </si>
+  <si>
+    <t>31_Rechnung_Staplermiete_HT-26-2214.pdf</t>
+  </si>
+  <si>
+    <t>PX-2026-6612</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>22.05.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>50771</t>
+  </si>
+  <si>
+    <t>PO-2026-12204</t>
+  </si>
+  <si>
+    <t>Palux Verpackungen GmbH</t>
+  </si>
+  <si>
+    <t>Transportverpackungen</t>
+  </si>
+  <si>
+    <t>09.06.2026</t>
+  </si>
+  <si>
+    <t>32_Rechnung_Transportverpackungen_PX-2026-6612.pdf</t>
+  </si>
+  <si>
+    <t>CL-2026-4471</t>
+  </si>
+  <si>
+    <t>13.02.2026</t>
+  </si>
+  <si>
+    <t>11.02.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>CL-6620</t>
+  </si>
+  <si>
+    <t>PO-2026-09117</t>
+  </si>
+  <si>
+    <t>Chemlab Laborbedarf GmbH</t>
+  </si>
+  <si>
+    <t>Laborbedarf und Chemikalien</t>
+  </si>
+  <si>
+    <t>06.03.2026</t>
+  </si>
+  <si>
+    <t>33_Rechnung_Laborbedarf_CL-2026-4471.pdf</t>
+  </si>
+  <si>
+    <t>MP-2026-0993</t>
+  </si>
+  <si>
+    <t>19.06.2026</t>
+  </si>
+  <si>
+    <t>15.06.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>MA-4410</t>
+  </si>
+  <si>
+    <t>Prüfbericht</t>
+  </si>
+  <si>
+    <t>PB-2026-0771</t>
+  </si>
+  <si>
+    <t>Materia Prüflabor GmbH</t>
+  </si>
+  <si>
+    <t>Materialprüfung</t>
+  </si>
+  <si>
+    <t>03.07.2026</t>
+  </si>
+  <si>
+    <t>34_Rechnung_Materialpruefung_MP-2026-0993.pdf</t>
+  </si>
+  <si>
+    <t>CZ-2026-0208</t>
+  </si>
+  <si>
+    <t>27.03.2026</t>
+  </si>
+  <si>
+    <t>23.03.2026 - 25.03.2026</t>
+  </si>
+  <si>
+    <t>CZ-1177</t>
+  </si>
+  <si>
+    <t>Zertifikat</t>
+  </si>
+  <si>
+    <t>ISO 9001:2015</t>
+  </si>
+  <si>
+    <t>Certum Zertifizierung GmbH</t>
+  </si>
+  <si>
+    <t>ISO-Zertifizierungsaudit</t>
+  </si>
+  <si>
+    <t>26.04.2026</t>
+  </si>
+  <si>
+    <t>35_Rechnung_ISO-Zertifizierungsaudit_CZ-2026-0208.pdf</t>
+  </si>
+  <si>
+    <t>VA-2026-0771</t>
+  </si>
+  <si>
+    <t>06.07.2026</t>
+  </si>
+  <si>
+    <t>VA-2288</t>
+  </si>
+  <si>
+    <t>Wartungsvertrag</t>
+  </si>
+  <si>
+    <t>WV-2021-17</t>
+  </si>
+  <si>
+    <t>Vertikal Aufzugservice GmbH</t>
+  </si>
+  <si>
+    <t>Aufzugswartung</t>
+  </si>
+  <si>
+    <t>27.07.2026</t>
+  </si>
+  <si>
+    <t>36_Rechnung_Aufzugswartung_VA-2026-0771.pdf</t>
+  </si>
+  <si>
+    <t>VE-2026-1188</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>04.05.2026 - 20.05.2026</t>
+  </si>
+  <si>
+    <t>VM-1409</t>
+  </si>
+  <si>
+    <t>A-2026-0774</t>
+  </si>
+  <si>
+    <t>Voltmann Elektrotechnik GmbH</t>
+  </si>
+  <si>
+    <t>Elektroinstallation Halle D</t>
+  </si>
+  <si>
+    <t>13.06.2026</t>
+  </si>
+  <si>
+    <t>37_Rechnung_Elektroinstallation_VE-2026-1188.pdf</t>
+  </si>
+  <si>
+    <t>FW-26-0339</t>
+  </si>
+  <si>
+    <t>17.07.2026</t>
+  </si>
+  <si>
+    <t>29.06.2026 - 14.07.2026</t>
+  </si>
+  <si>
+    <t>FW-880</t>
+  </si>
+  <si>
+    <t>A-26-1102</t>
+  </si>
+  <si>
+    <t>Farbwerk Malerbetrieb GmbH</t>
+  </si>
+  <si>
+    <t>Malerarbeiten Verwaltungsgebäude</t>
+  </si>
+  <si>
+    <t>07.08.2026</t>
+  </si>
+  <si>
+    <t>38_Rechnung_Malerarbeiten_FW-26-0339.pdf</t>
+  </si>
+  <si>
+    <t>GW-2026-0512</t>
+  </si>
+  <si>
+    <t>05.08.2026</t>
+  </si>
+  <si>
+    <t>01.07.2026 - 31.07.2026</t>
+  </si>
+  <si>
+    <t>GW-2255</t>
+  </si>
+  <si>
+    <t>Pflegevertrag</t>
+  </si>
+  <si>
+    <t>PV-2024-03</t>
+  </si>
+  <si>
+    <t>Grünwerk Gartenpflege GmbH</t>
+  </si>
+  <si>
+    <t>Pflege der Außenanlagen</t>
+  </si>
+  <si>
+    <t>19.08.2026</t>
+  </si>
+  <si>
+    <t>39_Rechnung_Pflege_GW-2026-0512.pdf</t>
+  </si>
+  <si>
+    <t>WD-2026-0044</t>
+  </si>
+  <si>
+    <t>02.02.2026</t>
+  </si>
+  <si>
+    <t>01.01.2026 - 31.01.2026</t>
+  </si>
+  <si>
+    <t>WF-1180</t>
+  </si>
+  <si>
+    <t>WD-2025-09</t>
+  </si>
+  <si>
+    <t>Winterfest Dienstleistungen GmbH</t>
+  </si>
+  <si>
+    <t>Winterdienst</t>
+  </si>
+  <si>
+    <t>16.02.2026</t>
+  </si>
+  <si>
+    <t>40_Rechnung_Winterdienst_WD-2026-0044.pdf</t>
+  </si>
+  <si>
+    <t>ST-2026-7719</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>08.06.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>51204</t>
+  </si>
+  <si>
+    <t>PO-2026-11907</t>
+  </si>
+  <si>
+    <t>Sensotec Messtechnik GmbH</t>
+  </si>
+  <si>
+    <t>Messtechnik Ersatzteile</t>
+  </si>
+  <si>
+    <t>10.07.2026</t>
+  </si>
+  <si>
+    <t>41_Rechnung_Messtechnik_ST-2026-7719.pdf</t>
+  </si>
+  <si>
+    <t>HF-26-3308</t>
+  </si>
+  <si>
+    <t>14.07.2026</t>
+  </si>
+  <si>
+    <t>10.07.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>50442</t>
+  </si>
+  <si>
+    <t>PO-2026-12771</t>
+  </si>
+  <si>
+    <t>Hydroflex Schlauchtechnik GmbH</t>
+  </si>
+  <si>
+    <t>Hydraulikschläuche und Armaturen</t>
+  </si>
+  <si>
+    <t>28.07.2026</t>
+  </si>
+  <si>
+    <t>42_Rechnung_Hydraulikschlaeuche_HF-26-3308.pdf</t>
+  </si>
+  <si>
+    <t>SK-2026-88117</t>
+  </si>
+  <si>
+    <t>21.02.2026</t>
+  </si>
+  <si>
+    <t>18.02.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>50881</t>
+  </si>
+  <si>
+    <t>PO-2026-09884</t>
+  </si>
+  <si>
+    <t>Stahlkontor Südwest GmbH</t>
+  </si>
+  <si>
+    <t>Stahlblech Rohmaterial</t>
+  </si>
+  <si>
+    <t>43_Rechnung_Stahlblech_SK-2026-88117.pdf</t>
+  </si>
+  <si>
+    <t>PM-2026-5504</t>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+  </si>
+  <si>
+    <t>27.03.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>50993</t>
+  </si>
+  <si>
+    <t>PO-2026-10118</t>
+  </si>
+  <si>
+    <t>Polymera Kunststoffhandel GmbH</t>
+  </si>
+  <si>
+    <t>Kunststoffgranulat</t>
+  </si>
+  <si>
+    <t>44_Rechnung_Kunststoffgranulat_PM-2026-5504.pdf</t>
+  </si>
+  <si>
+    <t>AS-2026-0117</t>
+  </si>
+  <si>
+    <t>08.01.2026</t>
+  </si>
+  <si>
+    <t>01.01.2026 - 31.12.2026 (Versicherungsperiode)</t>
+  </si>
+  <si>
+    <t>AS-3311</t>
+  </si>
+  <si>
+    <t>Policennummer</t>
+  </si>
+  <si>
+    <t>TV-2026-448120</t>
+  </si>
+  <si>
+    <t>Assekur Industriemakler GmbH</t>
+  </si>
+  <si>
+    <t>Transportversicherung</t>
+  </si>
+  <si>
+    <t>07.02.2026</t>
+  </si>
+  <si>
+    <t>45_Rechnung_Transportversicherung_AS-2026-0117.pdf</t>
+  </si>
+  <si>
+    <t>TA-2026-0662</t>
+  </si>
+  <si>
+    <t>25.06.2026</t>
+  </si>
+  <si>
+    <t>22.06.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>TA-1180</t>
+  </si>
+  <si>
+    <t>Vakanz</t>
+  </si>
+  <si>
+    <t>Leitung IT-Infrastruktur</t>
+  </si>
+  <si>
+    <t>Talentis Personalberatung GmbH</t>
+  </si>
+  <si>
+    <t>Personalvermittlung</t>
+  </si>
+  <si>
+    <t>46_Rechnung_Personalvermittlung_TA-2026-0662.pdf</t>
+  </si>
+  <si>
+    <t>EF-2026-2201</t>
+  </si>
+  <si>
+    <t>28.04.2026</t>
+  </si>
+  <si>
+    <t>24.04.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>EF-4402</t>
+  </si>
+  <si>
+    <t>PO-2026-10662</t>
+  </si>
+  <si>
+    <t>Ergoform Büroeinrichtung GmbH</t>
+  </si>
+  <si>
+    <t>Büromöbel und Ergonomie</t>
+  </si>
+  <si>
+    <t>19.05.2026</t>
+  </si>
+  <si>
+    <t>47_Rechnung_Bueromoebel_EF-2026-2201.pdf</t>
+  </si>
+  <si>
+    <t>AQ-2026-1104</t>
+  </si>
+  <si>
+    <t>04.06.2026</t>
+  </si>
+  <si>
+    <t>AQ-7714</t>
+  </si>
+  <si>
+    <t>SV-2023-22</t>
+  </si>
+  <si>
+    <t>Aquavit Wasserspender GmbH</t>
+  </si>
+  <si>
+    <t>Wasserspender und Kaffeeservice</t>
+  </si>
+  <si>
+    <t>18.06.2026</t>
+  </si>
+  <si>
+    <t>48_Rechnung_Wasserspender_AQ-2026-1104.pdf</t>
+  </si>
+  <si>
+    <t>VS-2026-0388</t>
+  </si>
+  <si>
+    <t>30.04.2026</t>
+  </si>
+  <si>
+    <t>10.02.2026 - 24.04.2026</t>
+  </si>
+  <si>
+    <t>VS-2019</t>
+  </si>
+  <si>
+    <t>Kursnummer</t>
+  </si>
+  <si>
+    <t>BE-2026-04</t>
+  </si>
+  <si>
+    <t>Verbal Sprachinstitut GmbH</t>
+  </si>
+  <si>
+    <t>Sprachkurse Business English</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>49_Rechnung_Sprachkurse_VS-2026-0388.pdf</t>
+  </si>
+  <si>
+    <t>B8-2026-0227</t>
+  </si>
+  <si>
+    <t>22.07.2026</t>
+  </si>
+  <si>
+    <t>06.07.2026 - 17.07.2026</t>
+  </si>
+  <si>
+    <t>B8-1150</t>
+  </si>
+  <si>
+    <t>Imagefilm Nachhaltigkeit</t>
+  </si>
+  <si>
+    <t>Blende8 Film und Foto GmbH</t>
+  </si>
+  <si>
+    <t>Imagefilm und Fotoproduktion</t>
+  </si>
+  <si>
+    <t>12.08.2026</t>
+  </si>
+  <si>
+    <t>50_Rechnung_Imagefilm_B8-2026-0227.pdf</t>
+  </si>
+  <si>
+    <t>FV-2026-0912</t>
+  </si>
+  <si>
+    <t>12.01.2026</t>
+  </si>
+  <si>
+    <t>AB-4471</t>
+  </si>
+  <si>
+    <t>Abonummer</t>
+  </si>
+  <si>
+    <t>A-99120</t>
+  </si>
+  <si>
+    <t>Fachpresse Verlag GmbH</t>
+  </si>
+  <si>
+    <t>Fachliteratur und Abonnements</t>
+  </si>
+  <si>
+    <t>51_Rechnung_Fachliteratur_FV-2026-0912.pdf</t>
+  </si>
+  <si>
+    <t>PR-2026-3341</t>
+  </si>
+  <si>
+    <t>18.02.2026</t>
+  </si>
+  <si>
+    <t>16.02.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>PM-2208</t>
+  </si>
+  <si>
+    <t>PO-2026-09441</t>
+  </si>
+  <si>
+    <t>Promota Werbemittel GmbH</t>
+  </si>
+  <si>
+    <t>Werbeartikel</t>
+  </si>
+  <si>
+    <t>04.03.2026</t>
+  </si>
+  <si>
+    <t>52_Rechnung_Werbeartikel_PR-2026-3341.pdf</t>
+  </si>
+  <si>
+    <t>KE-2026-11408</t>
+  </si>
+  <si>
+    <t>KE-3312</t>
+  </si>
+  <si>
+    <t>Sammelabrechnung</t>
+  </si>
+  <si>
+    <t>SA-2026-02</t>
+  </si>
+  <si>
+    <t>Kurierexpress Rhein-Neckar GmbH</t>
+  </si>
+  <si>
+    <t>Kurierfahrten</t>
+  </si>
+  <si>
+    <t>53_Rechnung_Kurierfahrten_KE-2026-11408.pdf</t>
+  </si>
+  <si>
+    <t>SD-2026-0448</t>
+  </si>
+  <si>
+    <t>07.04.2026</t>
+  </si>
+  <si>
+    <t>SD-1180</t>
+  </si>
+  <si>
+    <t>AV-2024-12</t>
+  </si>
+  <si>
+    <t>Sekurdoc Aktenservice GmbH</t>
+  </si>
+  <si>
+    <t>Aktenvernichtung und Archivierung</t>
+  </si>
+  <si>
+    <t>54_Rechnung_Aktenvernichtung_SD-2026-0448.pdf</t>
+  </si>
+  <si>
+    <t>IK-2026-0217</t>
+  </si>
+  <si>
+    <t>16.04.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>IK-2044</t>
+  </si>
+  <si>
+    <t>Gesellschafterversammlung</t>
+  </si>
+  <si>
+    <t>Interlingua Konferenzdienst GmbH</t>
+  </si>
+  <si>
+    <t>Dolmetscherdienst</t>
+  </si>
+  <si>
+    <t>05.05.2026</t>
+  </si>
+  <si>
+    <t>55_Rechnung_Dolmetscherdienst_IK-2026-0217.pdf</t>
+  </si>
+  <si>
+    <t>SA-2026-0331</t>
+  </si>
+  <si>
+    <t>06.05.2026</t>
+  </si>
+  <si>
+    <t>01.01.2026 - 31.03.2026</t>
+  </si>
+  <si>
+    <t>SI-7702</t>
+  </si>
+  <si>
+    <t>ASiG-2024-03</t>
+  </si>
+  <si>
+    <t>Sicura Arbeitsschutz Beratung GmbH</t>
+  </si>
+  <si>
+    <t>Arbeitssicherheit Betreuung</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>56_Rechnung_Arbeitssicherheit_SA-2026-0331.pdf</t>
+  </si>
+  <si>
+    <t>PS-2026-1104</t>
+  </si>
+  <si>
+    <t>13.05.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>PY-4402</t>
+  </si>
+  <si>
+    <t>A-2026-0882</t>
+  </si>
+  <si>
+    <t>Pyrostop Brandschutztechnik GmbH</t>
+  </si>
+  <si>
+    <t>Brandschutzwartung</t>
+  </si>
+  <si>
+    <t>57_Rechnung_Brandschutzwartung_PS-2026-1104.pdf</t>
+  </si>
+  <si>
+    <t>LW-2026-0662</t>
+  </si>
+  <si>
+    <t>02.06.2026</t>
+  </si>
+  <si>
+    <t>01.06.2026 - 31.05.2027</t>
+  </si>
+  <si>
+    <t>LW-3390</t>
+  </si>
+  <si>
+    <t>EL-2026-01</t>
+  </si>
+  <si>
+    <t>Lernwerk Digital GmbH</t>
+  </si>
+  <si>
+    <t>E-Learning Unterweisungen</t>
+  </si>
+  <si>
+    <t>02.07.2026</t>
+  </si>
+  <si>
+    <t>58_Rechnung_E-Learning_LW-2026-0662.pdf</t>
+  </si>
+  <si>
+    <t>AT-2026-0774</t>
+  </si>
+  <si>
+    <t>23.06.2026</t>
+  </si>
+  <si>
+    <t>18.06.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>AT-1150</t>
+  </si>
+  <si>
+    <t>A-26-2214</t>
+  </si>
+  <si>
+    <t>Airtec Drucklufttechnik GmbH</t>
+  </si>
+  <si>
+    <t>Druckluftanlagen Wartung</t>
+  </si>
+  <si>
+    <t>59_Rechnung_Druckluftanlagen_AT-2026-0774.pdf</t>
+  </si>
+  <si>
+    <t>WP-2026-8814</t>
+  </si>
+  <si>
+    <t>51180</t>
+  </si>
+  <si>
+    <t>PO-2026-12008</t>
+  </si>
+  <si>
+    <t>Weldpro Schweißtechnik GmbH</t>
+  </si>
+  <si>
+    <t>Schweißzusatzwerkstoffe</t>
+  </si>
+  <si>
+    <t>08.08.2026</t>
+  </si>
+  <si>
+    <t>60_Rechnung_Schweisszusatzwerkstoffe_WP-2026-8814.pdf</t>
+  </si>
+  <si>
+    <t>CO-2026-2219</t>
+  </si>
+  <si>
+    <t>13.07.2026 - 24.07.2026</t>
+  </si>
+  <si>
+    <t>CT-6620</t>
+  </si>
+  <si>
+    <t>PO-2026-12441</t>
+  </si>
+  <si>
+    <t>Coatec Oberflächentechnik GmbH</t>
+  </si>
+  <si>
+    <t>Lohnbeschichtung</t>
+  </si>
+  <si>
+    <t>17.08.2026</t>
+  </si>
+  <si>
+    <t>61_Rechnung_Lohnbeschichtung_CO-2026-2219.pdf</t>
+  </si>
+  <si>
+    <t>TH-2026-4471</t>
+  </si>
+  <si>
+    <t>31.07.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>TC-3308</t>
+  </si>
+  <si>
+    <t>PO-2026-12660</t>
+  </si>
+  <si>
+    <t>Thermica Härterei GmbH</t>
+  </si>
+  <si>
+    <t>Wärmebehandlung</t>
+  </si>
+  <si>
+    <t>04.09.2026</t>
+  </si>
+  <si>
+    <t>62_Rechnung_Waermebehandlung_TH-2026-4471.pdf</t>
+  </si>
+  <si>
+    <t>CT-2026-7719</t>
+  </si>
+  <si>
+    <t>12.08.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>PO-2026-12881</t>
+  </si>
+  <si>
+    <t>Cuttec Zerspanungswerkzeuge GmbH</t>
+  </si>
+  <si>
+    <t>Zerspanungswerkzeuge</t>
+  </si>
+  <si>
+    <t>63_Rechnung_Zerspanungswerkzeuge_CT-2026-7719.pdf</t>
+  </si>
+  <si>
+    <t>LM-2026-0338</t>
+  </si>
+  <si>
+    <t>01.09.2026</t>
+  </si>
+  <si>
+    <t>LX-2255</t>
+  </si>
+  <si>
+    <t>FM-2025-02</t>
+  </si>
+  <si>
+    <t>Lubrimax Fluidservice GmbH</t>
+  </si>
+  <si>
+    <t>Kühlschmierstoffmanagement</t>
+  </si>
+  <si>
+    <t>15.09.2026</t>
+  </si>
+  <si>
+    <t>64_Rechnung_Kuehlschmierstoffmanagement_LM-2026-0338.pdf</t>
+  </si>
+  <si>
+    <t>RX-2026-0114</t>
+  </si>
+  <si>
+    <t>11.09.2026</t>
+  </si>
+  <si>
+    <t>04.08.2026 - 05.09.2026</t>
+  </si>
+  <si>
+    <t>RB-1188</t>
+  </si>
+  <si>
+    <t>Handlingzelle Linie 4</t>
+  </si>
+  <si>
+    <t>Robotix Automation GmbH</t>
+  </si>
+  <si>
+    <t>Roboterintegration</t>
+  </si>
+  <si>
+    <t>11.10.2026</t>
+  </si>
+  <si>
+    <t>65_Rechnung_Roboterintegration_RX-2026-0114.pdf</t>
+  </si>
+  <si>
+    <t>SL-2026-0552</t>
+  </si>
+  <si>
+    <t>22.09.2026</t>
+  </si>
+  <si>
+    <t>01.09.2026 - 18.09.2026</t>
+  </si>
+  <si>
+    <t>SL-4409</t>
+  </si>
+  <si>
+    <t>A-2026-1180</t>
+  </si>
+  <si>
+    <t>Steuerlogik Systemtechnik GmbH</t>
+  </si>
+  <si>
+    <t>SPS-Programmierung</t>
+  </si>
+  <si>
+    <t>13.10.2026</t>
+  </si>
+  <si>
+    <t>66_Rechnung_SPS-Programmierung_SL-2026-0552.pdf</t>
+  </si>
+  <si>
+    <t>PT-2026-6640</t>
+  </si>
+  <si>
+    <t>28.09.2026</t>
+  </si>
+  <si>
+    <t>24.09.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>50662</t>
+  </si>
+  <si>
+    <t>PO-2026-13114</t>
+  </si>
+  <si>
+    <t>Pumptec Industrieservice GmbH</t>
+  </si>
+  <si>
+    <t>Pumpen Ersatzteile</t>
+  </si>
+  <si>
+    <t>28.10.2026</t>
+  </si>
+  <si>
+    <t>67_Rechnung_Pumpen_PT-2026-6640.pdf</t>
+  </si>
+  <si>
+    <t>LC-2026-0993</t>
+  </si>
+  <si>
+    <t>06.10.2026</t>
+  </si>
+  <si>
+    <t>28.09.2026 - 02.10.2026</t>
+  </si>
+  <si>
+    <t>LC-2044</t>
+  </si>
+  <si>
+    <t>PB-2026-1180</t>
+  </si>
+  <si>
+    <t>Liftcheck Prüfgesellschaft mbH</t>
+  </si>
+  <si>
+    <t>Kranprüfung UVV</t>
+  </si>
+  <si>
+    <t>27.10.2026</t>
+  </si>
+  <si>
+    <t>68_Rechnung_Kranpruefung_LC-2026-0993.pdf</t>
+  </si>
+  <si>
+    <t>RI-2026-0447</t>
+  </si>
+  <si>
+    <t>08.10.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>RI-3311</t>
+  </si>
+  <si>
+    <t>A-2026-1244</t>
+  </si>
+  <si>
+    <t>Rackinspect Lagertechnik GmbH</t>
+  </si>
+  <si>
+    <t>Regalinspektion</t>
+  </si>
+  <si>
+    <t>69_Rechnung_Regalinspektion_RI-2026-0447.pdf</t>
+  </si>
+  <si>
+    <t>MB-2026-1150</t>
+  </si>
+  <si>
+    <t>19.10.2026</t>
+  </si>
+  <si>
+    <t>01.09.2026 - 30.09.2026</t>
+  </si>
+  <si>
+    <t>MB-8804</t>
+  </si>
+  <si>
+    <t>MV-2026-14</t>
+  </si>
+  <si>
+    <t>Modulbau Raumsysteme GmbH</t>
+  </si>
+  <si>
+    <t>Baucontainer Miete</t>
+  </si>
+  <si>
+    <t>09.11.2026</t>
+  </si>
+  <si>
+    <t>70_Rechnung_Baucontainer_MB-2026-1150.pdf</t>
+  </si>
+  <si>
+    <t>BB-2026-0228</t>
+  </si>
+  <si>
+    <t>26.10.2026</t>
+  </si>
+  <si>
+    <t>21.09.2026 - 16.10.2026</t>
+  </si>
+  <si>
+    <t>BB-1102</t>
+  </si>
+  <si>
+    <t>A-2026-0991</t>
+  </si>
+  <si>
+    <t>Betonbau Südwest GmbH</t>
+  </si>
+  <si>
+    <t>Fundamentarbeiten</t>
+  </si>
+  <si>
+    <t>25.11.2026</t>
+  </si>
+  <si>
+    <t>71_Rechnung_Fundamentarbeiten_BB-2026-0228.pdf</t>
+  </si>
+  <si>
+    <t>DW-2026-0771</t>
+  </si>
+  <si>
+    <t>02.11.2026</t>
+  </si>
+  <si>
+    <t>05.10.2026 - 28.10.2026</t>
+  </si>
+  <si>
+    <t>DW-2210</t>
+  </si>
+  <si>
+    <t>A-2026-1088</t>
+  </si>
+  <si>
+    <t>Dachwerk Bedachungen GmbH</t>
+  </si>
+  <si>
+    <t>Dachsanierung</t>
+  </si>
+  <si>
+    <t>02.12.2026</t>
+  </si>
+  <si>
+    <t>72_Rechnung_Dachsanierung_DW-2026-0771.pdf</t>
+  </si>
+  <si>
+    <t>GK-2026-0338</t>
+  </si>
+  <si>
+    <t>19.10.2026 - 06.11.2026</t>
+  </si>
+  <si>
+    <t>GK-4402</t>
+  </si>
+  <si>
+    <t>A-2026-1177</t>
+  </si>
+  <si>
+    <t>Glasklar Fensterbau GmbH</t>
+  </si>
+  <si>
+    <t>Fensterbau und Verglasung</t>
+  </si>
+  <si>
+    <t>30.11.2026</t>
+  </si>
+  <si>
+    <t>73_Rechnung_Fensterbau_GK-2026-0338.pdf</t>
+  </si>
+  <si>
+    <t>LW-2026-2204</t>
+  </si>
+  <si>
+    <t>16.11.2026</t>
+  </si>
+  <si>
+    <t>11.11.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>LK-6612</t>
+  </si>
+  <si>
+    <t>PO-2026-13440</t>
+  </si>
+  <si>
+    <t>Lockwell Schließsysteme GmbH</t>
+  </si>
+  <si>
+    <t>Zutrittskontrolle</t>
+  </si>
+  <si>
+    <t>07.12.2026</t>
+  </si>
+  <si>
+    <t>74_Rechnung_Zutrittskontrolle_LW-2026-2204.pdf</t>
+  </si>
+  <si>
+    <t>VT-2026-0885</t>
+  </si>
+  <si>
+    <t>23.11.2026</t>
+  </si>
+  <si>
+    <t>18.11.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>VS-3390</t>
+  </si>
+  <si>
+    <t>PO-2026-13511</t>
+  </si>
+  <si>
+    <t>Visiotec Sicherheitstechnik GmbH</t>
+  </si>
+  <si>
+    <t>Videoueberwachung</t>
+  </si>
+  <si>
+    <t>23.12.2026</t>
+  </si>
+  <si>
+    <t>75_Rechnung_Videoueberwachung_VT-2026-0885.pdf</t>
+  </si>
+  <si>
+    <t>FN-2026-4417</t>
+  </si>
+  <si>
+    <t>02.11.2026 - 25.11.2026</t>
+  </si>
+  <si>
+    <t>FN-1204</t>
+  </si>
+  <si>
+    <t>Standortanbindung Werk 3</t>
+  </si>
+  <si>
+    <t>Fibernet Infrastruktur GmbH</t>
+  </si>
+  <si>
+    <t>Glasfaseranschluss</t>
+  </si>
+  <si>
+    <t>30.12.2026</t>
+  </si>
+  <si>
+    <t>76_Rechnung_Glasfaseranschluss_FN-2026-4417.pdf</t>
+  </si>
+  <si>
+    <t>SX-2026-0662</t>
+  </si>
+  <si>
+    <t>03.12.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>SX-8811</t>
+  </si>
+  <si>
+    <t>AN-2026-0447</t>
+  </si>
+  <si>
+    <t>Storix Datensysteme GmbH</t>
+  </si>
+  <si>
+    <t>Storage-System</t>
+  </si>
+  <si>
+    <t>27.12.2026</t>
+  </si>
+  <si>
+    <t>77_Rechnung_Storage-System_SX-2026-0662.pdf</t>
+  </si>
+  <si>
+    <t>EC-2026-11840</t>
+  </si>
+  <si>
+    <t>14.12.2026</t>
+  </si>
+  <si>
+    <t>01.11.2026 - 30.11.2026</t>
+  </si>
+  <si>
+    <t>EC-2019</t>
+  </si>
+  <si>
+    <t>AMS-2025-04</t>
+  </si>
+  <si>
+    <t>ERPcare Servicegesellschaft mbH</t>
+  </si>
+  <si>
+    <t>SAP-Wartung und Support</t>
+  </si>
+  <si>
+    <t>04.01.2027</t>
+  </si>
+  <si>
+    <t>78_Rechnung_SAP-Wartung_EC-2026-11840.pdf</t>
+  </si>
+  <si>
+    <t>DH-2026-0774</t>
+  </si>
+  <si>
+    <t>01.01.2026 - 31.12.2026</t>
+  </si>
+  <si>
+    <t>DB-4471</t>
+  </si>
+  <si>
+    <t>AN-2025-8814</t>
+  </si>
+  <si>
+    <t>Datenbankhaus Vertriebs GmbH</t>
+  </si>
+  <si>
+    <t>Datenbanklizenzen</t>
+  </si>
+  <si>
+    <t>79_Rechnung_Datenbanklizenzen_DH-2026-0774.pdf</t>
+  </si>
+  <si>
+    <t>CB-2026-0117</t>
+  </si>
+  <si>
+    <t>26.01.2026</t>
+  </si>
+  <si>
+    <t>12.01.2026 - 23.01.2026</t>
+  </si>
+  <si>
+    <t>CS-3302</t>
+  </si>
+  <si>
+    <t>Pentest Produktionsnetz</t>
+  </si>
+  <si>
+    <t>Cybershield Security GmbH</t>
+  </si>
+  <si>
+    <t>IT-Security Penetrationstest</t>
+  </si>
+  <si>
+    <t>09.02.2026</t>
+  </si>
+  <si>
+    <t>80_Rechnung_IT-Security_CB-2026-0117.pdf</t>
+  </si>
+  <si>
+    <t>PF-2026-0338</t>
+  </si>
+  <si>
+    <t>04.02.2026</t>
+  </si>
+  <si>
+    <t>PF-1180</t>
+  </si>
+  <si>
+    <t>MPS-2024-08</t>
+  </si>
+  <si>
+    <t>Printflow Bueroservice GmbH</t>
+  </si>
+  <si>
+    <t>Managed Print Services</t>
+  </si>
+  <si>
+    <t>81_Rechnung_Managed_PF-2026-0338.pdf</t>
+  </si>
+  <si>
+    <t>VC-2026-2214</t>
+  </si>
+  <si>
+    <t>11.02.2026</t>
+  </si>
+  <si>
+    <t>05.02.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>VC-7714</t>
+  </si>
+  <si>
+    <t>PO-2026-09660</t>
+  </si>
+  <si>
+    <t>Voicecom Kommunikationssysteme GmbH</t>
+  </si>
+  <si>
+    <t>Telefonanlage UCC</t>
+  </si>
+  <si>
+    <t>82_Rechnung_Telefonanlage_VC-2026-2214.pdf</t>
+  </si>
+  <si>
+    <t>MV-2026-0093</t>
+  </si>
+  <si>
+    <t>05.01.2026 - 13.02.2026</t>
+  </si>
+  <si>
+    <t>MV-2288</t>
+  </si>
+  <si>
+    <t>Studie Reinigungsmarkt EU</t>
+  </si>
+  <si>
+    <t>Markview Marktforschung GmbH</t>
+  </si>
+  <si>
+    <t>Marktforschungsstudie</t>
+  </si>
+  <si>
+    <t>11.03.2026</t>
+  </si>
+  <si>
+    <t>83_Rechnung_Marktforschungsstudie_MV-2026-0093.pdf</t>
+  </si>
+  <si>
+    <t>SG-2026-0441</t>
+  </si>
+  <si>
+    <t>25.02.2026</t>
+  </si>
+  <si>
+    <t>01.02.2026 - 20.02.2026</t>
+  </si>
+  <si>
+    <t>SG-1104</t>
+  </si>
+  <si>
+    <t>Portfolioanalyse 2030</t>
+  </si>
+  <si>
+    <t>Strategika Unternehmensberatung GmbH</t>
+  </si>
+  <si>
+    <t>Strategieberatung</t>
+  </si>
+  <si>
+    <t>84_Rechnung_Strategieberatung_SG-2026-0441.pdf</t>
+  </si>
+  <si>
+    <t>KP-2026-0662</t>
+  </si>
+  <si>
+    <t>16.02.2026 - 01.03.2026</t>
+  </si>
+  <si>
+    <t>KP-3311</t>
+  </si>
+  <si>
+    <t>KW 08 und 09</t>
+  </si>
+  <si>
+    <t>Kontor Personalservice GmbH</t>
+  </si>
+  <si>
+    <t>Zeitarbeit kaufmännisch</t>
+  </si>
+  <si>
+    <t>18.03.2026</t>
+  </si>
+  <si>
+    <t>85_Rechnung_Zeitarbeit_KP-2026-0662.pdf</t>
+  </si>
+  <si>
+    <t>UP-2026-0227</t>
+  </si>
+  <si>
+    <t>12.03.2026</t>
+  </si>
+  <si>
+    <t>27.02.2026 - 08.03.2026</t>
+  </si>
+  <si>
+    <t>UP-4409</t>
+  </si>
+  <si>
+    <t>A-2026-0338</t>
+  </si>
+  <si>
+    <t>Umzugsprofis Rhein-Neckar GmbH</t>
+  </si>
+  <si>
+    <t>Betriebsumzug</t>
+  </si>
+  <si>
+    <t>86_Rechnung_Betriebsumzug_UP-2026-0227.pdf</t>
+  </si>
+  <si>
+    <t>HF-2026-0118</t>
+  </si>
+  <si>
+    <t>19.03.2026</t>
+  </si>
+  <si>
+    <t>23.02.2026 - 13.03.2026</t>
+  </si>
+  <si>
+    <t>HF-2201</t>
+  </si>
+  <si>
+    <t>A-2026-0442</t>
+  </si>
+  <si>
+    <t>Holzform Objekttischlerei GmbH</t>
+  </si>
+  <si>
+    <t>Sondermöbelbau</t>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+  </si>
+  <si>
+    <t>87_Rechnung_Sondermoebelbau_HF-2026-0118.pdf</t>
+  </si>
+  <si>
+    <t>SG-2026-1180</t>
+  </si>
+  <si>
+    <t>26.03.2026</t>
+  </si>
+  <si>
+    <t>20.03.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>ST-5511</t>
+  </si>
+  <si>
+    <t>A-2026-0551</t>
+  </si>
+  <si>
+    <t>Signaltechnik Werbedesign GmbH</t>
+  </si>
+  <si>
+    <t>Beschilderung</t>
+  </si>
+  <si>
+    <t>16.04.2026</t>
+  </si>
+  <si>
+    <t>88_Rechnung_Beschilderung_SG-2026-1180.pdf</t>
+  </si>
+  <si>
+    <t>RL-2026-0552</t>
+  </si>
+  <si>
+    <t>23.03.2026 - 27.03.2026</t>
+  </si>
+  <si>
+    <t>RL-1140</t>
+  </si>
+  <si>
+    <t>PB-2026-0338</t>
+  </si>
+  <si>
+    <t>Radiolab Prüftechnik GmbH</t>
+  </si>
+  <si>
+    <t>Zerstörungsfreie Prüfung</t>
+  </si>
+  <si>
+    <t>23.04.2026</t>
+  </si>
+  <si>
+    <t>89_Rechnung_Zerstoerungsfreie_RL-2026-0552.pdf</t>
+  </si>
+  <si>
+    <t>CR-2026-0338</t>
+  </si>
+  <si>
+    <t>01.04.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>CR-2255</t>
+  </si>
+  <si>
+    <t>RR-2024-07</t>
+  </si>
+  <si>
+    <t>Cleanroom Systems GmbH</t>
+  </si>
+  <si>
+    <t>Reinraumwartung</t>
+  </si>
+  <si>
+    <t>90_Rechnung_Reinraumwartung_CR-2026-0338.pdf</t>
+  </si>
+  <si>
+    <t>HL-2026-0771</t>
+  </si>
+  <si>
+    <t>06.04.2026 - 10.04.2026</t>
+  </si>
+  <si>
+    <t>HL-3308</t>
+  </si>
+  <si>
+    <t>PB-2026-0447</t>
+  </si>
+  <si>
+    <t>Hydrolab Wasseranalytik GmbH</t>
+  </si>
+  <si>
+    <t>Trinkwasseranalyse</t>
+  </si>
+  <si>
+    <t>91_Rechnung_Trinkwasseranalyse_HL-2026-0771.pdf</t>
+  </si>
+  <si>
+    <t>VI-2026-0448</t>
+  </si>
+  <si>
+    <t>VI-1188</t>
+  </si>
+  <si>
+    <t>SB-2023-05</t>
+  </si>
+  <si>
+    <t>Vitalis Schädlingsbekämpfung GmbH</t>
+  </si>
+  <si>
+    <t>Schädlingsmonitoring</t>
+  </si>
+  <si>
+    <t>92_Rechnung_Schaedlingsmonitoring_VI-2026-0448.pdf</t>
+  </si>
+  <si>
+    <t>RZ-2026-2204</t>
+  </si>
+  <si>
+    <t>13.04.2026 - 24.04.2026</t>
+  </si>
+  <si>
+    <t>RZ-4471</t>
+  </si>
+  <si>
+    <t>FL-2025-11</t>
+  </si>
+  <si>
+    <t>Reifenzentrum Südwest GmbH</t>
+  </si>
+  <si>
+    <t>Reifenservice Fuhrpark</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>93_Rechnung_Reifenservice_RZ-2026-2204.pdf</t>
+  </si>
+  <si>
+    <t>TP-2026-88410</t>
+  </si>
+  <si>
+    <t>TP-1204</t>
+  </si>
+  <si>
+    <t>Kartenkreis</t>
+  </si>
+  <si>
+    <t>FK-2026-114</t>
+  </si>
+  <si>
+    <t>Tankpartner Kraftstoffe GmbH</t>
+  </si>
+  <si>
+    <t>Kraftstoff Tankkarten</t>
+  </si>
+  <si>
+    <t>94_Rechnung_Kraftstoff_TP-2026-88410.pdf</t>
+  </si>
+  <si>
+    <t>FM-2026-1140</t>
+  </si>
+  <si>
+    <t>FX-2019</t>
+  </si>
+  <si>
+    <t>MW-2025-06</t>
+  </si>
+  <si>
+    <t>Flexmobil Autovermietung GmbH</t>
+  </si>
+  <si>
+    <t>Mietwagen Langzeitmiete</t>
+  </si>
+  <si>
+    <t>95_Rechnung_Mietwagen_FM-2026-1140.pdf</t>
+  </si>
+  <si>
+    <t>LP-2026-3390</t>
+  </si>
+  <si>
+    <t>18.05.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>51330</t>
+  </si>
+  <si>
+    <t>PO-2026-11220</t>
+  </si>
+  <si>
+    <t>Labelpro Kennzeichnungstechnik GmbH</t>
+  </si>
+  <si>
+    <t>Etiketten und Kennzeichnung</t>
+  </si>
+  <si>
+    <t>96_Rechnung_Etiketten_LP-2026-3390.pdf</t>
+  </si>
+  <si>
+    <t>WB-2026-0338</t>
+  </si>
+  <si>
+    <t>WB-2255</t>
+  </si>
+  <si>
+    <t>WV-2024-02</t>
+  </si>
+  <si>
+    <t>Werksbus Verkehrsbetrieb GmbH</t>
+  </si>
+  <si>
+    <t>Werksbusverkehr</t>
+  </si>
+  <si>
+    <t>97_Rechnung_Werksbusverkehr_WB-2026-0338.pdf</t>
+  </si>
+  <si>
+    <t>FW-2026-0771</t>
+  </si>
+  <si>
+    <t>30.05.2026 (Leistungsdatum)</t>
+  </si>
+  <si>
+    <t>FE-3311</t>
+  </si>
+  <si>
+    <t>Sommerfest 2026</t>
+  </si>
+  <si>
+    <t>Festwerk Eventagentur GmbH</t>
+  </si>
+  <si>
+    <t>Sommerfest Betriebsfeier</t>
+  </si>
+  <si>
+    <t>98_Rechnung_Sommerfest_FW-2026-0771.pdf</t>
+  </si>
+  <si>
+    <t>KP-2026-4471</t>
+  </si>
+  <si>
+    <t>51442</t>
+  </si>
+  <si>
+    <t>Klimapartner Gerätetechnik GmbH</t>
+  </si>
+  <si>
+    <t>Klimageräte Beschaffung</t>
+  </si>
+  <si>
+    <t>11.07.2026</t>
+  </si>
+  <si>
+    <t>99_Rechnung_Klimageraete_KP-2026-4471.pdf</t>
+  </si>
+  <si>
+    <t>PT-2026-5518</t>
+  </si>
+  <si>
+    <t>51550</t>
+  </si>
+  <si>
+    <t>PO-2026-11991</t>
+  </si>
+  <si>
+    <t>Protega Arbeitsschutz GmbH</t>
+  </si>
+  <si>
+    <t>Persönliche Schutzausrüstung</t>
+  </si>
+  <si>
+    <t>100_Rechnung_Persoenliche_PT-2026-5518.pdf</t>
+  </si>
+  <si>
+    <t>Summe</t>
+  </si>
+  <si>
+    <t>Legende:</t>
+  </si>
+  <si>
+    <t>Blaue Schrift = Wert aus der Original-Rechnung (Netto, Steuersatz)</t>
+  </si>
+  <si>
+    <t>Schwarze Schrift = berechnet (USt = Netto x Steuersatz, Brutto = Netto + USt)</t>
+  </si>
+  <si>
+    <t>Zeilen 2-12: Rechnungen 01-11 | 13-51: Rechnungen 12-50 | 52-101: Rechnungen 51-100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2691,80 +2705,56 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2788,14 +2778,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -2810,150 +2800,59 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
-      <top style="thin"/>
-      <bottom style="double"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F3864"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -3012,51 +2911,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3064,12 +2975,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -3098,7 +3009,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -3119,7 +3030,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -3170,7 +3081,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -3188,40 +3099,39 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O108"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="44"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3268,7 +3178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -3296,18 +3206,18 @@
       <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="5">
         <v>3372</v>
       </c>
-      <c r="K2" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L2" s="7" t="n">
-        <f aca="false">ROUND(J2*K2,2)</f>
-        <v>640.68</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <f aca="false">ROUND(J2+L2,2)</f>
+      <c r="K2" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L2" s="7">
+        <f t="shared" ref="L2:L33" si="0">ROUND(J2*K2,2)</f>
+        <v>640.67999999999995</v>
+      </c>
+      <c r="M2" s="8">
+        <f t="shared" ref="M2:M33" si="1">ROUND(J2+L2,2)</f>
         <v>4012.68</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -3317,7 +3227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -3345,18 +3255,18 @@
       <c r="I3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="5">
         <v>4878</v>
       </c>
-      <c r="K3" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L3" s="7" t="n">
-        <f aca="false">ROUND(J3*K3,2)</f>
+      <c r="K3" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" si="0"/>
         <v>926.82</v>
       </c>
-      <c r="M3" s="8" t="n">
-        <f aca="false">ROUND(J3+L3,2)</f>
+      <c r="M3" s="8">
+        <f t="shared" si="1"/>
         <v>5804.82</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -3366,7 +3276,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -3394,19 +3304,19 @@
       <c r="I4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>26930</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <f aca="false">ROUND(J4*K4,2)</f>
-        <v>5116.7</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <f aca="false">ROUND(J4+L4,2)</f>
-        <v>32046.7</v>
+      <c r="J4" s="5">
+        <v>36930</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="0"/>
+        <v>7016.7</v>
+      </c>
+      <c r="M4" s="8">
+        <f>ROUND(J4+L4,2)</f>
+        <v>43946.7</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>45</v>
@@ -3415,7 +3325,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -3441,18 +3351,18 @@
       <c r="I5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="5">
         <v>3913.4</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <f aca="false">ROUND(J5*K5,2)</f>
+      <c r="K5" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="0"/>
         <v>743.55</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <f aca="false">ROUND(J5+L5,2)</f>
+      <c r="M5" s="8">
+        <f t="shared" si="1"/>
         <v>4656.95</v>
       </c>
       <c r="N5" s="3" t="s">
@@ -3462,7 +3372,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
@@ -3490,18 +3400,18 @@
       <c r="I6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>4595.15</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <f aca="false">ROUND(J6*K6,2)</f>
+      <c r="J6" s="5">
+        <v>4595.1499999999996</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="0"/>
         <v>873.08</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <f aca="false">ROUND(J6+L6,2)</f>
+      <c r="M6" s="8">
+        <f t="shared" si="1"/>
         <v>5468.23</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -3511,7 +3421,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>68</v>
       </c>
@@ -3539,18 +3449,18 @@
       <c r="I7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="5">
         <v>28806</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <f aca="false">ROUND(J7*K7,2)</f>
+      <c r="K7" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="0"/>
         <v>5473.14</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <f aca="false">ROUND(J7+L7,2)</f>
+      <c r="M7" s="8">
+        <f t="shared" si="1"/>
         <v>34279.14</v>
       </c>
       <c r="N7" s="3" t="s">
@@ -3560,7 +3470,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -3588,18 +3498,18 @@
       <c r="I8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="5">
         <v>12980</v>
       </c>
-      <c r="K8" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <f aca="false">ROUND(J8*K8,2)</f>
-        <v>2466.2</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <f aca="false">ROUND(J8+L8,2)</f>
+      <c r="K8" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="0"/>
+        <v>2466.1999999999998</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" si="1"/>
         <v>15446.2</v>
       </c>
       <c r="N8" s="3" t="s">
@@ -3609,7 +3519,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>88</v>
       </c>
@@ -3637,18 +3547,18 @@
       <c r="I9" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="5">
         <v>6629</v>
       </c>
-      <c r="K9" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <f aca="false">ROUND(J9*K9,2)</f>
+      <c r="K9" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="0"/>
         <v>1259.51</v>
       </c>
-      <c r="M9" s="8" t="n">
-        <f aca="false">ROUND(J9+L9,2)</f>
+      <c r="M9" s="8">
+        <f t="shared" si="1"/>
         <v>7888.51</v>
       </c>
       <c r="N9" s="3" t="s">
@@ -3658,7 +3568,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
@@ -3686,18 +3596,18 @@
       <c r="I10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="5">
         <v>8715</v>
       </c>
-      <c r="K10" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <f aca="false">ROUND(J10*K10,2)</f>
+      <c r="K10" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" si="0"/>
         <v>1655.85</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <f aca="false">ROUND(J10+L10,2)</f>
+      <c r="M10" s="8">
+        <f t="shared" si="1"/>
         <v>10370.85</v>
       </c>
       <c r="N10" s="3" t="s">
@@ -3707,7 +3617,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -3735,18 +3645,18 @@
       <c r="I11" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="5">
         <v>27282</v>
       </c>
-      <c r="K11" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <f aca="false">ROUND(J11*K11,2)</f>
+      <c r="K11" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="0"/>
         <v>5183.58</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <f aca="false">ROUND(J11+L11,2)</f>
+      <c r="M11" s="8">
+        <f t="shared" si="1"/>
         <v>32465.58</v>
       </c>
       <c r="N11" s="3" t="s">
@@ -3756,7 +3666,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>57</v>
       </c>
@@ -3784,18 +3694,18 @@
       <c r="I12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <v>20142.4</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <f aca="false">ROUND(J12*K12,2)</f>
+      <c r="J12" s="5">
+        <v>20142.400000000001</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="0"/>
         <v>3827.06</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <f aca="false">ROUND(J12+L12,2)</f>
+      <c r="M12" s="8">
+        <f t="shared" si="1"/>
         <v>23969.46</v>
       </c>
       <c r="N12" s="3" t="s">
@@ -3805,7 +3715,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
@@ -3833,18 +3743,18 @@
       <c r="I13" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="5">
         <v>132549</v>
       </c>
-      <c r="K13" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L13" s="7" t="n">
-        <f aca="false">ROUND(J13*K13,2)</f>
+      <c r="K13" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="0"/>
         <v>25184.31</v>
       </c>
-      <c r="M13" s="8" t="n">
-        <f aca="false">ROUND(J13+L13,2)</f>
+      <c r="M13" s="8">
+        <f t="shared" si="1"/>
         <v>157733.31</v>
       </c>
       <c r="N13" s="3" t="s">
@@ -3854,7 +3764,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>88</v>
       </c>
@@ -3882,18 +3792,18 @@
       <c r="I14" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="J14" s="5" t="n">
-        <v>48610.4</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <f aca="false">ROUND(J14*K14,2)</f>
+      <c r="J14" s="5">
+        <v>48610.400000000001</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="0"/>
         <v>9235.98</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <f aca="false">ROUND(J14+L14,2)</f>
+      <c r="M14" s="8">
+        <f t="shared" si="1"/>
         <v>57846.38</v>
       </c>
       <c r="N14" s="3" t="s">
@@ -3903,7 +3813,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -3931,18 +3841,18 @@
       <c r="I15" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="5">
         <v>11671.6</v>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <f aca="false">ROUND(J15*K15,2)</f>
+      <c r="K15" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="0"/>
         <v>2217.6</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <f aca="false">ROUND(J15+L15,2)</f>
+      <c r="M15" s="8">
+        <f t="shared" si="1"/>
         <v>13889.2</v>
       </c>
       <c r="N15" s="3" t="s">
@@ -3952,7 +3862,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -3980,18 +3890,18 @@
       <c r="I16" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="5">
         <v>86244</v>
       </c>
-      <c r="K16" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L16" s="7" t="n">
-        <f aca="false">ROUND(J16*K16,2)</f>
+      <c r="K16" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="0"/>
         <v>16386.36</v>
       </c>
-      <c r="M16" s="8" t="n">
-        <f aca="false">ROUND(J16+L16,2)</f>
+      <c r="M16" s="8">
+        <f t="shared" si="1"/>
         <v>102630.36</v>
       </c>
       <c r="N16" s="3" t="s">
@@ -4001,7 +3911,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -4029,18 +3939,18 @@
       <c r="I17" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="5">
         <v>24130</v>
       </c>
-      <c r="K17" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <f aca="false">ROUND(J17*K17,2)</f>
+      <c r="K17" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="0"/>
         <v>4584.7</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <f aca="false">ROUND(J17+L17,2)</f>
+      <c r="M17" s="8">
+        <f t="shared" si="1"/>
         <v>28714.7</v>
       </c>
       <c r="N17" s="3" t="s">
@@ -4050,7 +3960,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>172</v>
       </c>
@@ -4078,18 +3988,18 @@
       <c r="I18" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J18" s="5">
         <v>5549</v>
       </c>
-      <c r="K18" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <f aca="false">ROUND(J18*K18,2)</f>
+      <c r="K18" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="0"/>
         <v>1054.31</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <f aca="false">ROUND(J18+L18,2)</f>
+      <c r="M18" s="8">
+        <f t="shared" si="1"/>
         <v>6603.31</v>
       </c>
       <c r="N18" s="3" t="s">
@@ -4099,7 +4009,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>88</v>
       </c>
@@ -4127,18 +4037,18 @@
       <c r="I19" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>5163.6</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <f aca="false">ROUND(J19*K19,2)</f>
+      <c r="J19" s="5">
+        <v>5163.6000000000004</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="0"/>
         <v>981.08</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <f aca="false">ROUND(J19+L19,2)</f>
+      <c r="M19" s="8">
+        <f t="shared" si="1"/>
         <v>6144.68</v>
       </c>
       <c r="N19" s="3" t="s">
@@ -4148,7 +4058,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
@@ -4176,18 +4086,18 @@
       <c r="I20" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J20" s="5">
         <v>2698.4</v>
       </c>
-      <c r="K20" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <f aca="false">ROUND(J20*K20,2)</f>
-        <v>512.7</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <f aca="false">ROUND(J20+L20,2)</f>
+      <c r="K20" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="0"/>
+        <v>512.70000000000005</v>
+      </c>
+      <c r="M20" s="8">
+        <f t="shared" si="1"/>
         <v>3211.1</v>
       </c>
       <c r="N20" s="3" t="s">
@@ -4197,7 +4107,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>15</v>
       </c>
@@ -4225,18 +4135,18 @@
       <c r="I21" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J21" s="5">
         <v>25323</v>
       </c>
-      <c r="K21" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L21" s="7" t="n">
-        <f aca="false">ROUND(J21*K21,2)</f>
+      <c r="K21" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="0"/>
         <v>4811.37</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <f aca="false">ROUND(J21+L21,2)</f>
+      <c r="M21" s="8">
+        <f t="shared" si="1"/>
         <v>30134.37</v>
       </c>
       <c r="N21" s="3" t="s">
@@ -4246,7 +4156,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
@@ -4274,18 +4184,18 @@
       <c r="I22" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="5">
         <v>15872</v>
       </c>
-      <c r="K22" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <f aca="false">ROUND(J22*K22,2)</f>
+      <c r="K22" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="0"/>
         <v>3015.68</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <f aca="false">ROUND(J22+L22,2)</f>
+      <c r="M22" s="8">
+        <f t="shared" si="1"/>
         <v>18887.68</v>
       </c>
       <c r="N22" s="3" t="s">
@@ -4295,7 +4205,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>15</v>
       </c>
@@ -4323,19 +4233,19 @@
       <c r="I23" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="5">
         <v>32630</v>
       </c>
-      <c r="K23" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L23" s="7" t="n">
-        <f aca="false">ROUND(J23*K23,2)</f>
+      <c r="K23" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="0"/>
         <v>6199.7</v>
       </c>
-      <c r="M23" s="8" t="n">
-        <f aca="false">ROUND(J23+L23,2)</f>
-        <v>38829.7</v>
+      <c r="M23" s="8">
+        <f t="shared" si="1"/>
+        <v>38829.699999999997</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>225</v>
@@ -4344,7 +4254,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
@@ -4372,19 +4282,19 @@
       <c r="I24" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="5">
         <v>56160</v>
       </c>
-      <c r="K24" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <f aca="false">ROUND(J24*K24,2)</f>
+      <c r="K24" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="0"/>
         <v>10670.4</v>
       </c>
-      <c r="M24" s="8" t="n">
-        <f aca="false">ROUND(J24+L24,2)</f>
-        <v>66830.4</v>
+      <c r="M24" s="8">
+        <f t="shared" si="1"/>
+        <v>66830.399999999994</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>235</v>
@@ -4393,7 +4303,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
@@ -4421,18 +4331,18 @@
       <c r="I25" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="5">
         <v>5305</v>
       </c>
-      <c r="K25" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <f aca="false">ROUND(J25*K25,2)</f>
+      <c r="K25" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="0"/>
         <v>1007.95</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <f aca="false">ROUND(J25+L25,2)</f>
+      <c r="M25" s="8">
+        <f t="shared" si="1"/>
         <v>6312.95</v>
       </c>
       <c r="N25" s="3" t="s">
@@ -4442,7 +4352,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>88</v>
       </c>
@@ -4470,18 +4380,18 @@
       <c r="I26" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J26" s="5">
         <v>11794</v>
       </c>
-      <c r="K26" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <f aca="false">ROUND(J26*K26,2)</f>
+      <c r="K26" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="0"/>
         <v>2240.86</v>
       </c>
-      <c r="M26" s="8" t="n">
-        <f aca="false">ROUND(J26+L26,2)</f>
+      <c r="M26" s="8">
+        <f t="shared" si="1"/>
         <v>14034.86</v>
       </c>
       <c r="N26" s="3" t="s">
@@ -4491,7 +4401,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
@@ -4519,18 +4429,18 @@
       <c r="I27" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="5">
         <v>20204</v>
       </c>
-      <c r="K27" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <f aca="false">ROUND(J27*K27,2)</f>
+      <c r="K27" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="0"/>
         <v>3838.76</v>
       </c>
-      <c r="M27" s="8" t="n">
-        <f aca="false">ROUND(J27+L27,2)</f>
+      <c r="M27" s="8">
+        <f t="shared" si="1"/>
         <v>24042.76</v>
       </c>
       <c r="N27" s="3" t="s">
@@ -4540,7 +4450,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>68</v>
       </c>
@@ -4568,19 +4478,19 @@
       <c r="I28" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="5">
         <v>48720</v>
       </c>
-      <c r="K28" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <f aca="false">ROUND(J28*K28,2)</f>
-        <v>9256.8</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <f aca="false">ROUND(J28+L28,2)</f>
-        <v>57976.8</v>
+      <c r="K28" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="0"/>
+        <v>9256.7999999999993</v>
+      </c>
+      <c r="M28" s="8">
+        <f t="shared" si="1"/>
+        <v>57976.800000000003</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>269</v>
@@ -4589,7 +4499,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>47</v>
       </c>
@@ -4617,18 +4527,18 @@
       <c r="I29" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="5">
         <v>216400</v>
       </c>
-      <c r="K29" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <f aca="false">ROUND(J29*K29,2)</f>
+      <c r="K29" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="0"/>
         <v>41116</v>
       </c>
-      <c r="M29" s="8" t="n">
-        <f aca="false">ROUND(J29+L29,2)</f>
+      <c r="M29" s="8">
+        <f t="shared" si="1"/>
         <v>257516</v>
       </c>
       <c r="N29" s="3" t="s">
@@ -4638,7 +4548,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
@@ -4666,19 +4576,19 @@
       <c r="I30" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="5">
         <v>18440</v>
       </c>
-      <c r="K30" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <f aca="false">ROUND(J30*K30,2)</f>
+      <c r="K30" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L30" s="7">
+        <f t="shared" si="0"/>
         <v>3503.6</v>
       </c>
-      <c r="M30" s="8" t="n">
-        <f aca="false">ROUND(J30+L30,2)</f>
-        <v>21943.6</v>
+      <c r="M30" s="8">
+        <f t="shared" si="1"/>
+        <v>21943.599999999999</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>286</v>
@@ -4687,7 +4597,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>57</v>
       </c>
@@ -4715,18 +4625,18 @@
       <c r="I31" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="J31" s="5" t="n">
-        <v>27033.6</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L31" s="7" t="n">
-        <f aca="false">ROUND(J31*K31,2)</f>
+      <c r="J31" s="5">
+        <v>27033.599999999999</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="0"/>
         <v>5136.38</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <f aca="false">ROUND(J31+L31,2)</f>
+      <c r="M31" s="8">
+        <f t="shared" si="1"/>
         <v>32169.98</v>
       </c>
       <c r="N31" s="3" t="s">
@@ -4736,7 +4646,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>57</v>
       </c>
@@ -4764,18 +4674,18 @@
       <c r="I32" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J32" s="5">
         <v>15394</v>
       </c>
-      <c r="K32" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <f aca="false">ROUND(J32*K32,2)</f>
+      <c r="K32" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L32" s="7">
+        <f t="shared" si="0"/>
         <v>2924.86</v>
       </c>
-      <c r="M32" s="8" t="n">
-        <f aca="false">ROUND(J32+L32,2)</f>
+      <c r="M32" s="8">
+        <f t="shared" si="1"/>
         <v>18318.86</v>
       </c>
       <c r="N32" s="3" t="s">
@@ -4785,7 +4695,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>88</v>
       </c>
@@ -4813,18 +4723,18 @@
       <c r="I33" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="5">
         <v>16986</v>
       </c>
-      <c r="K33" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L33" s="7" t="n">
-        <f aca="false">ROUND(J33*K33,2)</f>
+      <c r="K33" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="0"/>
         <v>3227.34</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <f aca="false">ROUND(J33+L33,2)</f>
+      <c r="M33" s="8">
+        <f t="shared" si="1"/>
         <v>20213.34</v>
       </c>
       <c r="N33" s="3" t="s">
@@ -4834,7 +4744,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>172</v>
       </c>
@@ -4862,18 +4772,18 @@
       <c r="I34" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J34" s="5">
         <v>4905.2</v>
       </c>
-      <c r="K34" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L34" s="7" t="n">
-        <f aca="false">ROUND(J34*K34,2)</f>
+      <c r="K34" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L34" s="7">
+        <f t="shared" ref="L34:L65" si="2">ROUND(J34*K34,2)</f>
         <v>931.99</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <f aca="false">ROUND(J34+L34,2)</f>
+      <c r="M34" s="8">
+        <f t="shared" ref="M34:M65" si="3">ROUND(J34+L34,2)</f>
         <v>5837.19</v>
       </c>
       <c r="N34" s="3" t="s">
@@ -4883,7 +4793,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>47</v>
       </c>
@@ -4911,18 +4821,18 @@
       <c r="I35" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="5">
         <v>11928</v>
       </c>
-      <c r="K35" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L35" s="7" t="n">
-        <f aca="false">ROUND(J35*K35,2)</f>
-        <v>2266.32</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <f aca="false">ROUND(J35+L35,2)</f>
+      <c r="K35" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L35" s="7">
+        <f t="shared" si="2"/>
+        <v>2266.3200000000002</v>
+      </c>
+      <c r="M35" s="8">
+        <f t="shared" si="3"/>
         <v>14194.32</v>
       </c>
       <c r="N35" s="3" t="s">
@@ -4932,7 +4842,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>88</v>
       </c>
@@ -4960,18 +4870,18 @@
       <c r="I36" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="J36" s="5">
         <v>11070</v>
       </c>
-      <c r="K36" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L36" s="7" t="n">
-        <f aca="false">ROUND(J36*K36,2)</f>
-        <v>2103.3</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <f aca="false">ROUND(J36+L36,2)</f>
+      <c r="K36" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="2"/>
+        <v>2103.3000000000002</v>
+      </c>
+      <c r="M36" s="8">
+        <f t="shared" si="3"/>
         <v>13173.3</v>
       </c>
       <c r="N36" s="3" t="s">
@@ -4981,7 +4891,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -5009,18 +4919,18 @@
       <c r="I37" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="J37" s="5">
         <v>5144</v>
       </c>
-      <c r="K37" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L37" s="7" t="n">
-        <f aca="false">ROUND(J37*K37,2)</f>
+      <c r="K37" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="2"/>
         <v>977.36</v>
       </c>
-      <c r="M37" s="8" t="n">
-        <f aca="false">ROUND(J37+L37,2)</f>
+      <c r="M37" s="8">
+        <f t="shared" si="3"/>
         <v>6121.36</v>
       </c>
       <c r="N37" s="3" t="s">
@@ -5030,7 +4940,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>47</v>
       </c>
@@ -5058,18 +4968,18 @@
       <c r="I38" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J38" s="5">
         <v>33334</v>
       </c>
-      <c r="K38" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L38" s="7" t="n">
-        <f aca="false">ROUND(J38*K38,2)</f>
+      <c r="K38" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L38" s="7">
+        <f t="shared" si="2"/>
         <v>6333.46</v>
       </c>
-      <c r="M38" s="8" t="n">
-        <f aca="false">ROUND(J38+L38,2)</f>
+      <c r="M38" s="8">
+        <f t="shared" si="3"/>
         <v>39667.46</v>
       </c>
       <c r="N38" s="3" t="s">
@@ -5079,7 +4989,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>15</v>
       </c>
@@ -5107,18 +5017,18 @@
       <c r="I39" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="J39" s="5">
         <v>33362</v>
       </c>
-      <c r="K39" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L39" s="7" t="n">
-        <f aca="false">ROUND(J39*K39,2)</f>
+      <c r="K39" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L39" s="7">
+        <f t="shared" si="2"/>
         <v>6338.78</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <f aca="false">ROUND(J39+L39,2)</f>
+      <c r="M39" s="8">
+        <f t="shared" si="3"/>
         <v>39700.78</v>
       </c>
       <c r="N39" s="3" t="s">
@@ -5128,7 +5038,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>57</v>
       </c>
@@ -5156,18 +5066,18 @@
       <c r="I40" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="J40" s="5">
         <v>7556</v>
       </c>
-      <c r="K40" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L40" s="7" t="n">
-        <f aca="false">ROUND(J40*K40,2)</f>
+      <c r="K40" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L40" s="7">
+        <f t="shared" si="2"/>
         <v>1435.64</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <f aca="false">ROUND(J40+L40,2)</f>
+      <c r="M40" s="8">
+        <f t="shared" si="3"/>
         <v>8991.64</v>
       </c>
       <c r="N40" s="3" t="s">
@@ -5177,7 +5087,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>47</v>
       </c>
@@ -5205,18 +5115,18 @@
       <c r="I41" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="J41" s="5">
         <v>12268</v>
       </c>
-      <c r="K41" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L41" s="7" t="n">
-        <f aca="false">ROUND(J41*K41,2)</f>
+      <c r="K41" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L41" s="7">
+        <f t="shared" si="2"/>
         <v>2330.92</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <f aca="false">ROUND(J41+L41,2)</f>
+      <c r="M41" s="8">
+        <f t="shared" si="3"/>
         <v>14598.92</v>
       </c>
       <c r="N41" s="3" t="s">
@@ -5226,7 +5136,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>47</v>
       </c>
@@ -5254,18 +5164,18 @@
       <c r="I42" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="J42" s="5">
         <v>11097.6</v>
       </c>
-      <c r="K42" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L42" s="7" t="n">
-        <f aca="false">ROUND(J42*K42,2)</f>
+      <c r="K42" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L42" s="7">
+        <f t="shared" si="2"/>
         <v>2108.54</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <f aca="false">ROUND(J42+L42,2)</f>
+      <c r="M42" s="8">
+        <f t="shared" si="3"/>
         <v>13206.14</v>
       </c>
       <c r="N42" s="3" t="s">
@@ -5275,7 +5185,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>88</v>
       </c>
@@ -5303,18 +5213,18 @@
       <c r="I43" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="J43" s="5">
         <v>11826</v>
       </c>
-      <c r="K43" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L43" s="7" t="n">
-        <f aca="false">ROUND(J43*K43,2)</f>
+      <c r="K43" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L43" s="7">
+        <f t="shared" si="2"/>
         <v>2246.94</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <f aca="false">ROUND(J43+L43,2)</f>
+      <c r="M43" s="8">
+        <f t="shared" si="3"/>
         <v>14072.94</v>
       </c>
       <c r="N43" s="3" t="s">
@@ -5324,7 +5234,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>88</v>
       </c>
@@ -5352,18 +5262,18 @@
       <c r="I44" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="J44" s="5">
         <v>39872</v>
       </c>
-      <c r="K44" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L44" s="7" t="n">
-        <f aca="false">ROUND(J44*K44,2)</f>
+      <c r="K44" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L44" s="7">
+        <f t="shared" si="2"/>
         <v>7575.68</v>
       </c>
-      <c r="M44" s="8" t="n">
-        <f aca="false">ROUND(J44+L44,2)</f>
+      <c r="M44" s="8">
+        <f t="shared" si="3"/>
         <v>47447.68</v>
       </c>
       <c r="N44" s="3" t="s">
@@ -5373,7 +5283,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>88</v>
       </c>
@@ -5401,19 +5311,19 @@
       <c r="I45" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="J45" s="5" t="n">
+      <c r="J45" s="5">
         <v>72480</v>
       </c>
-      <c r="K45" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L45" s="7" t="n">
-        <f aca="false">ROUND(J45*K45,2)</f>
+      <c r="K45" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L45" s="7">
+        <f t="shared" si="2"/>
         <v>13771.2</v>
       </c>
-      <c r="M45" s="8" t="n">
-        <f aca="false">ROUND(J45+L45,2)</f>
-        <v>86251.2</v>
+      <c r="M45" s="8">
+        <f t="shared" si="3"/>
+        <v>86251.199999999997</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>174</v>
@@ -5422,7 +5332,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>15</v>
       </c>
@@ -5450,18 +5360,18 @@
       <c r="I46" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="J46" s="5">
         <v>33000</v>
       </c>
-      <c r="K46" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L46" s="7" t="n">
-        <f aca="false">ROUND(J46*K46,2)</f>
+      <c r="K46" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L46" s="7">
+        <f t="shared" si="2"/>
         <v>6270</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <f aca="false">ROUND(J46+L46,2)</f>
+      <c r="M46" s="8">
+        <f t="shared" si="3"/>
         <v>39270</v>
       </c>
       <c r="N46" s="3" t="s">
@@ -5471,7 +5381,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
@@ -5499,18 +5409,18 @@
       <c r="I47" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="J47" s="5" t="n">
+      <c r="J47" s="5">
         <v>35050</v>
       </c>
-      <c r="K47" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L47" s="7" t="n">
-        <f aca="false">ROUND(J47*K47,2)</f>
+      <c r="K47" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L47" s="7">
+        <f t="shared" si="2"/>
         <v>6659.5</v>
       </c>
-      <c r="M47" s="8" t="n">
-        <f aca="false">ROUND(J47+L47,2)</f>
+      <c r="M47" s="8">
+        <f t="shared" si="3"/>
         <v>41709.5</v>
       </c>
       <c r="N47" s="3" t="s">
@@ -5520,7 +5430,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>15</v>
       </c>
@@ -5548,18 +5458,18 @@
       <c r="I48" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="J48" s="5">
         <v>93624</v>
       </c>
-      <c r="K48" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L48" s="7" t="n">
-        <f aca="false">ROUND(J48*K48,2)</f>
-        <v>17788.56</v>
-      </c>
-      <c r="M48" s="8" t="n">
-        <f aca="false">ROUND(J48+L48,2)</f>
+      <c r="K48" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L48" s="7">
+        <f t="shared" si="2"/>
+        <v>17788.560000000001</v>
+      </c>
+      <c r="M48" s="8">
+        <f t="shared" si="3"/>
         <v>111412.56</v>
       </c>
       <c r="N48" s="3" t="s">
@@ -5569,7 +5479,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>57</v>
       </c>
@@ -5597,18 +5507,18 @@
       <c r="I49" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="J49" s="5" t="n">
+      <c r="J49" s="5">
         <v>7228</v>
       </c>
-      <c r="K49" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L49" s="7" t="n">
-        <f aca="false">ROUND(J49*K49,2)</f>
+      <c r="K49" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L49" s="7">
+        <f t="shared" si="2"/>
         <v>1373.32</v>
       </c>
-      <c r="M49" s="8" t="n">
-        <f aca="false">ROUND(J49+L49,2)</f>
+      <c r="M49" s="8">
+        <f t="shared" si="3"/>
         <v>8601.32</v>
       </c>
       <c r="N49" s="3" t="s">
@@ -5618,7 +5528,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>172</v>
       </c>
@@ -5646,19 +5556,19 @@
       <c r="I50" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="J50" s="5" t="n">
+      <c r="J50" s="5">
         <v>24384</v>
       </c>
-      <c r="K50" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L50" s="7" t="n">
-        <f aca="false">ROUND(J50*K50,2)</f>
+      <c r="K50" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L50" s="7">
+        <f t="shared" si="2"/>
         <v>4632.96</v>
       </c>
-      <c r="M50" s="8" t="n">
-        <f aca="false">ROUND(J50+L50,2)</f>
-        <v>29016.96</v>
+      <c r="M50" s="8">
+        <f t="shared" si="3"/>
+        <v>29016.959999999999</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>467</v>
@@ -5667,7 +5577,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>68</v>
       </c>
@@ -5695,18 +5605,18 @@
       <c r="I51" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="J51" s="5" t="n">
+      <c r="J51" s="5">
         <v>40400</v>
       </c>
-      <c r="K51" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L51" s="7" t="n">
-        <f aca="false">ROUND(J51*K51,2)</f>
+      <c r="K51" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L51" s="7">
+        <f t="shared" si="2"/>
         <v>7676</v>
       </c>
-      <c r="M51" s="8" t="n">
-        <f aca="false">ROUND(J51+L51,2)</f>
+      <c r="M51" s="8">
+        <f t="shared" si="3"/>
         <v>48076</v>
       </c>
       <c r="N51" s="3" t="s">
@@ -5716,7 +5626,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>47</v>
       </c>
@@ -5744,18 +5654,18 @@
       <c r="I52" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="J52" s="5">
         <v>16072</v>
       </c>
-      <c r="K52" s="6" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="L52" s="7" t="n">
-        <f aca="false">ROUND(J52*K52,2)</f>
+      <c r="K52" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L52" s="7">
+        <f t="shared" si="2"/>
         <v>1125.04</v>
       </c>
-      <c r="M52" s="8" t="n">
-        <f aca="false">ROUND(J52+L52,2)</f>
+      <c r="M52" s="8">
+        <f t="shared" si="3"/>
         <v>17197.04</v>
       </c>
       <c r="N52" s="3" t="s">
@@ -5765,7 +5675,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>68</v>
       </c>
@@ -5793,18 +5703,18 @@
       <c r="I53" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="J53" s="5" t="n">
+      <c r="J53" s="5">
         <v>23900</v>
       </c>
-      <c r="K53" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L53" s="7" t="n">
-        <f aca="false">ROUND(J53*K53,2)</f>
+      <c r="K53" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L53" s="7">
+        <f t="shared" si="2"/>
         <v>4541</v>
       </c>
-      <c r="M53" s="8" t="n">
-        <f aca="false">ROUND(J53+L53,2)</f>
+      <c r="M53" s="8">
+        <f t="shared" si="3"/>
         <v>28441</v>
       </c>
       <c r="N53" s="3" t="s">
@@ -5814,7 +5724,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>47</v>
       </c>
@@ -5842,18 +5752,18 @@
       <c r="I54" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="J54" s="5" t="n">
+      <c r="J54" s="5">
         <v>9513</v>
       </c>
-      <c r="K54" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L54" s="7" t="n">
-        <f aca="false">ROUND(J54*K54,2)</f>
+      <c r="K54" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L54" s="7">
+        <f t="shared" si="2"/>
         <v>1807.47</v>
       </c>
-      <c r="M54" s="8" t="n">
-        <f aca="false">ROUND(J54+L54,2)</f>
+      <c r="M54" s="8">
+        <f t="shared" si="3"/>
         <v>11320.47</v>
       </c>
       <c r="N54" s="3" t="s">
@@ -5863,7 +5773,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>15</v>
       </c>
@@ -5891,18 +5801,18 @@
       <c r="I55" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="J55" s="5" t="n">
+      <c r="J55" s="5">
         <v>3400</v>
       </c>
-      <c r="K55" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L55" s="7" t="n">
-        <f aca="false">ROUND(J55*K55,2)</f>
+      <c r="K55" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L55" s="7">
+        <f t="shared" si="2"/>
         <v>646</v>
       </c>
-      <c r="M55" s="8" t="n">
-        <f aca="false">ROUND(J55+L55,2)</f>
+      <c r="M55" s="8">
+        <f t="shared" si="3"/>
         <v>4046</v>
       </c>
       <c r="N55" s="3" t="s">
@@ -5912,7 +5822,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>15</v>
       </c>
@@ -5940,18 +5850,18 @@
       <c r="I56" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="J56" s="5" t="n">
+      <c r="J56" s="5">
         <v>10610</v>
       </c>
-      <c r="K56" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L56" s="7" t="n">
-        <f aca="false">ROUND(J56*K56,2)</f>
+      <c r="K56" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L56" s="7">
+        <f t="shared" si="2"/>
         <v>2015.9</v>
       </c>
-      <c r="M56" s="8" t="n">
-        <f aca="false">ROUND(J56+L56,2)</f>
+      <c r="M56" s="8">
+        <f t="shared" si="3"/>
         <v>12625.9</v>
       </c>
       <c r="N56" s="3" t="s">
@@ -5961,7 +5871,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>88</v>
       </c>
@@ -5989,18 +5899,18 @@
       <c r="I57" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="J57" s="5" t="n">
+      <c r="J57" s="5">
         <v>16152</v>
       </c>
-      <c r="K57" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L57" s="7" t="n">
-        <f aca="false">ROUND(J57*K57,2)</f>
+      <c r="K57" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L57" s="7">
+        <f t="shared" si="2"/>
         <v>3068.88</v>
       </c>
-      <c r="M57" s="8" t="n">
-        <f aca="false">ROUND(J57+L57,2)</f>
+      <c r="M57" s="8">
+        <f t="shared" si="3"/>
         <v>19220.88</v>
       </c>
       <c r="N57" s="3" t="s">
@@ -6010,7 +5920,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>57</v>
       </c>
@@ -6038,18 +5948,18 @@
       <c r="I58" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="J58" s="5" t="n">
+      <c r="J58" s="5">
         <v>11835.2</v>
       </c>
-      <c r="K58" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L58" s="7" t="n">
-        <f aca="false">ROUND(J58*K58,2)</f>
+      <c r="K58" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L58" s="7">
+        <f t="shared" si="2"/>
         <v>2248.69</v>
       </c>
-      <c r="M58" s="8" t="n">
-        <f aca="false">ROUND(J58+L58,2)</f>
+      <c r="M58" s="8">
+        <f t="shared" si="3"/>
         <v>14083.89</v>
       </c>
       <c r="N58" s="3" t="s">
@@ -6059,7 +5969,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>36</v>
       </c>
@@ -6087,18 +5997,18 @@
       <c r="I59" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="J59" s="5" t="n">
+      <c r="J59" s="5">
         <v>51960</v>
       </c>
-      <c r="K59" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L59" s="7" t="n">
-        <f aca="false">ROUND(J59*K59,2)</f>
+      <c r="K59" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L59" s="7">
+        <f t="shared" si="2"/>
         <v>9872.4</v>
       </c>
-      <c r="M59" s="8" t="n">
-        <f aca="false">ROUND(J59+L59,2)</f>
+      <c r="M59" s="8">
+        <f t="shared" si="3"/>
         <v>61832.4</v>
       </c>
       <c r="N59" s="3" t="s">
@@ -6108,7 +6018,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>88</v>
       </c>
@@ -6136,18 +6046,18 @@
       <c r="I60" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="J60" s="5" t="n">
+      <c r="J60" s="5">
         <v>9658</v>
       </c>
-      <c r="K60" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L60" s="7" t="n">
-        <f aca="false">ROUND(J60*K60,2)</f>
+      <c r="K60" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L60" s="7">
+        <f t="shared" si="2"/>
         <v>1835.02</v>
       </c>
-      <c r="M60" s="8" t="n">
-        <f aca="false">ROUND(J60+L60,2)</f>
+      <c r="M60" s="8">
+        <f t="shared" si="3"/>
         <v>11493.02</v>
       </c>
       <c r="N60" s="3" t="s">
@@ -6157,7 +6067,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>47</v>
       </c>
@@ -6185,18 +6095,18 @@
       <c r="I61" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="J61" s="5" t="n">
+      <c r="J61" s="5">
         <v>9858</v>
       </c>
-      <c r="K61" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L61" s="7" t="n">
-        <f aca="false">ROUND(J61*K61,2)</f>
+      <c r="K61" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L61" s="7">
+        <f t="shared" si="2"/>
         <v>1873.02</v>
       </c>
-      <c r="M61" s="8" t="n">
-        <f aca="false">ROUND(J61+L61,2)</f>
+      <c r="M61" s="8">
+        <f t="shared" si="3"/>
         <v>11731.02</v>
       </c>
       <c r="N61" s="3" t="s">
@@ -6206,7 +6116,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>88</v>
       </c>
@@ -6234,19 +6144,19 @@
       <c r="I62" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="J62" s="5" t="n">
+      <c r="J62" s="5">
         <v>30488</v>
       </c>
-      <c r="K62" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L62" s="7" t="n">
-        <f aca="false">ROUND(J62*K62,2)</f>
+      <c r="K62" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L62" s="7">
+        <f t="shared" si="2"/>
         <v>5792.72</v>
       </c>
-      <c r="M62" s="8" t="n">
-        <f aca="false">ROUND(J62+L62,2)</f>
-        <v>36280.72</v>
+      <c r="M62" s="8">
+        <f t="shared" si="3"/>
+        <v>36280.720000000001</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>563</v>
@@ -6255,7 +6165,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>47</v>
       </c>
@@ -6283,18 +6193,18 @@
       <c r="I63" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="J63" s="5" t="n">
+      <c r="J63" s="5">
         <v>11744</v>
       </c>
-      <c r="K63" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L63" s="7" t="n">
-        <f aca="false">ROUND(J63*K63,2)</f>
+      <c r="K63" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L63" s="7">
+        <f t="shared" si="2"/>
         <v>2231.36</v>
       </c>
-      <c r="M63" s="8" t="n">
-        <f aca="false">ROUND(J63+L63,2)</f>
+      <c r="M63" s="8">
+        <f t="shared" si="3"/>
         <v>13975.36</v>
       </c>
       <c r="N63" s="3" t="s">
@@ -6304,7 +6214,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>47</v>
       </c>
@@ -6332,19 +6242,19 @@
       <c r="I64" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="J64" s="5" t="n">
+      <c r="J64" s="5">
         <v>32160</v>
       </c>
-      <c r="K64" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L64" s="7" t="n">
-        <f aca="false">ROUND(J64*K64,2)</f>
+      <c r="K64" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L64" s="7">
+        <f t="shared" si="2"/>
         <v>6110.4</v>
       </c>
-      <c r="M64" s="8" t="n">
-        <f aca="false">ROUND(J64+L64,2)</f>
-        <v>38270.4</v>
+      <c r="M64" s="8">
+        <f t="shared" si="3"/>
+        <v>38270.400000000001</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>571</v>
@@ -6353,7 +6263,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>88</v>
       </c>
@@ -6381,18 +6291,18 @@
       <c r="I65" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="J65" s="5" t="n">
+      <c r="J65" s="5">
         <v>15592.4</v>
       </c>
-      <c r="K65" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L65" s="7" t="n">
-        <f aca="false">ROUND(J65*K65,2)</f>
+      <c r="K65" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L65" s="7">
+        <f t="shared" si="2"/>
         <v>2962.56</v>
       </c>
-      <c r="M65" s="8" t="n">
-        <f aca="false">ROUND(J65+L65,2)</f>
+      <c r="M65" s="8">
+        <f t="shared" si="3"/>
         <v>18554.96</v>
       </c>
       <c r="N65" s="3" t="s">
@@ -6402,7 +6312,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>47</v>
       </c>
@@ -6430,18 +6340,18 @@
       <c r="I66" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J66" s="5" t="n">
+      <c r="J66" s="5">
         <v>164104</v>
       </c>
-      <c r="K66" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L66" s="7" t="n">
-        <f aca="false">ROUND(J66*K66,2)</f>
-        <v>31179.76</v>
-      </c>
-      <c r="M66" s="8" t="n">
-        <f aca="false">ROUND(J66+L66,2)</f>
+      <c r="K66" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L66" s="7">
+        <f t="shared" ref="L66:L97" si="4">ROUND(J66*K66,2)</f>
+        <v>31179.759999999998</v>
+      </c>
+      <c r="M66" s="8">
+        <f t="shared" ref="M66:M97" si="5">ROUND(J66+L66,2)</f>
         <v>195283.76</v>
       </c>
       <c r="N66" s="3" t="s">
@@ -6451,7 +6361,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>57</v>
       </c>
@@ -6479,19 +6389,19 @@
       <c r="I67" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="J67" s="5" t="n">
+      <c r="J67" s="5">
         <v>47952</v>
       </c>
-      <c r="K67" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L67" s="7" t="n">
-        <f aca="false">ROUND(J67*K67,2)</f>
-        <v>9110.88</v>
-      </c>
-      <c r="M67" s="8" t="n">
-        <f aca="false">ROUND(J67+L67,2)</f>
-        <v>57062.88</v>
+      <c r="K67" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L67" s="7">
+        <f t="shared" si="4"/>
+        <v>9110.8799999999992</v>
+      </c>
+      <c r="M67" s="8">
+        <f t="shared" si="5"/>
+        <v>57062.879999999997</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>603</v>
@@ -6500,7 +6410,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>88</v>
       </c>
@@ -6528,19 +6438,19 @@
       <c r="I68" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="J68" s="5" t="n">
+      <c r="J68" s="5">
         <v>20760</v>
       </c>
-      <c r="K68" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L68" s="7" t="n">
-        <f aca="false">ROUND(J68*K68,2)</f>
+      <c r="K68" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L68" s="7">
+        <f t="shared" si="4"/>
         <v>3944.4</v>
       </c>
-      <c r="M68" s="8" t="n">
-        <f aca="false">ROUND(J68+L68,2)</f>
-        <v>24704.4</v>
+      <c r="M68" s="8">
+        <f t="shared" si="5"/>
+        <v>24704.400000000001</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>612</v>
@@ -6549,7 +6459,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>47</v>
       </c>
@@ -6577,18 +6487,18 @@
       <c r="I69" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="J69" s="5" t="n">
+      <c r="J69" s="5">
         <v>12060</v>
       </c>
-      <c r="K69" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L69" s="7" t="n">
-        <f aca="false">ROUND(J69*K69,2)</f>
+      <c r="K69" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L69" s="7">
+        <f t="shared" si="4"/>
         <v>2291.4</v>
       </c>
-      <c r="M69" s="8" t="n">
-        <f aca="false">ROUND(J69+L69,2)</f>
+      <c r="M69" s="8">
+        <f t="shared" si="5"/>
         <v>14351.4</v>
       </c>
       <c r="N69" s="3" t="s">
@@ -6598,7 +6508,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>57</v>
       </c>
@@ -6626,18 +6536,18 @@
       <c r="I70" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="J70" s="5" t="n">
+      <c r="J70" s="5">
         <v>10716</v>
       </c>
-      <c r="K70" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L70" s="7" t="n">
-        <f aca="false">ROUND(J70*K70,2)</f>
+      <c r="K70" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L70" s="7">
+        <f t="shared" si="4"/>
         <v>2036.04</v>
       </c>
-      <c r="M70" s="8" t="n">
-        <f aca="false">ROUND(J70+L70,2)</f>
+      <c r="M70" s="8">
+        <f t="shared" si="5"/>
         <v>12752.04</v>
       </c>
       <c r="N70" s="3" t="s">
@@ -6647,7 +6557,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>88</v>
       </c>
@@ -6675,18 +6585,18 @@
       <c r="I71" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="J71" s="5" t="n">
+      <c r="J71" s="5">
         <v>6080</v>
       </c>
-      <c r="K71" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L71" s="7" t="n">
-        <f aca="false">ROUND(J71*K71,2)</f>
+      <c r="K71" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L71" s="7">
+        <f t="shared" si="4"/>
         <v>1155.2</v>
       </c>
-      <c r="M71" s="8" t="n">
-        <f aca="false">ROUND(J71+L71,2)</f>
+      <c r="M71" s="8">
+        <f t="shared" si="5"/>
         <v>7235.2</v>
       </c>
       <c r="N71" s="3" t="s">
@@ -6696,7 +6606,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>47</v>
       </c>
@@ -6724,18 +6634,18 @@
       <c r="I72" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="J72" s="5" t="n">
+      <c r="J72" s="5">
         <v>96544</v>
       </c>
-      <c r="K72" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L72" s="7" t="n">
-        <f aca="false">ROUND(J72*K72,2)</f>
+      <c r="K72" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L72" s="7">
+        <f t="shared" si="4"/>
         <v>18343.36</v>
       </c>
-      <c r="M72" s="8" t="n">
-        <f aca="false">ROUND(J72+L72,2)</f>
+      <c r="M72" s="8">
+        <f t="shared" si="5"/>
         <v>114887.36</v>
       </c>
       <c r="N72" s="3" t="s">
@@ -6745,7 +6655,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>57</v>
       </c>
@@ -6773,18 +6683,18 @@
       <c r="I73" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="J73" s="5" t="n">
+      <c r="J73" s="5">
         <v>206280</v>
       </c>
-      <c r="K73" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L73" s="7" t="n">
-        <f aca="false">ROUND(J73*K73,2)</f>
-        <v>39193.2</v>
-      </c>
-      <c r="M73" s="8" t="n">
-        <f aca="false">ROUND(J73+L73,2)</f>
+      <c r="K73" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L73" s="7">
+        <f t="shared" si="4"/>
+        <v>39193.199999999997</v>
+      </c>
+      <c r="M73" s="8">
+        <f t="shared" si="5"/>
         <v>245473.2</v>
       </c>
       <c r="N73" s="3" t="s">
@@ -6794,7 +6704,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>15</v>
       </c>
@@ -6822,18 +6732,18 @@
       <c r="I74" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="J74" s="5" t="n">
+      <c r="J74" s="5">
         <v>87064</v>
       </c>
-      <c r="K74" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L74" s="7" t="n">
-        <f aca="false">ROUND(J74*K74,2)</f>
+      <c r="K74" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L74" s="7">
+        <f t="shared" si="4"/>
         <v>16542.16</v>
       </c>
-      <c r="M74" s="8" t="n">
-        <f aca="false">ROUND(J74+L74,2)</f>
+      <c r="M74" s="8">
+        <f t="shared" si="5"/>
         <v>103606.16</v>
       </c>
       <c r="N74" s="3" t="s">
@@ -6843,7 +6753,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>36</v>
       </c>
@@ -6871,19 +6781,19 @@
       <c r="I75" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="J75" s="5" t="n">
+      <c r="J75" s="5">
         <v>51520</v>
       </c>
-      <c r="K75" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L75" s="7" t="n">
-        <f aca="false">ROUND(J75*K75,2)</f>
-        <v>9788.8</v>
-      </c>
-      <c r="M75" s="8" t="n">
-        <f aca="false">ROUND(J75+L75,2)</f>
-        <v>61308.8</v>
+      <c r="K75" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L75" s="7">
+        <f t="shared" si="4"/>
+        <v>9788.7999999999993</v>
+      </c>
+      <c r="M75" s="8">
+        <f t="shared" si="5"/>
+        <v>61308.800000000003</v>
       </c>
       <c r="N75" s="3" t="s">
         <v>672</v>
@@ -6892,7 +6802,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>57</v>
       </c>
@@ -6920,18 +6830,18 @@
       <c r="I76" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="J76" s="5" t="n">
+      <c r="J76" s="5">
         <v>52340</v>
       </c>
-      <c r="K76" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L76" s="7" t="n">
-        <f aca="false">ROUND(J76*K76,2)</f>
+      <c r="K76" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L76" s="7">
+        <f t="shared" si="4"/>
         <v>9944.6</v>
       </c>
-      <c r="M76" s="8" t="n">
-        <f aca="false">ROUND(J76+L76,2)</f>
+      <c r="M76" s="8">
+        <f t="shared" si="5"/>
         <v>62284.6</v>
       </c>
       <c r="N76" s="3" t="s">
@@ -6941,7 +6851,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>36</v>
       </c>
@@ -6969,18 +6879,18 @@
       <c r="I77" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="J77" s="5" t="n">
+      <c r="J77" s="5">
         <v>97208</v>
       </c>
-      <c r="K77" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L77" s="7" t="n">
-        <f aca="false">ROUND(J77*K77,2)</f>
+      <c r="K77" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L77" s="7">
+        <f t="shared" si="4"/>
         <v>18469.52</v>
       </c>
-      <c r="M77" s="8" t="n">
-        <f aca="false">ROUND(J77+L77,2)</f>
+      <c r="M77" s="8">
+        <f t="shared" si="5"/>
         <v>115677.52</v>
       </c>
       <c r="N77" s="3" t="s">
@@ -6990,7 +6900,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>36</v>
       </c>
@@ -7018,18 +6928,18 @@
       <c r="I78" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="J78" s="5" t="n">
+      <c r="J78" s="5">
         <v>233800</v>
       </c>
-      <c r="K78" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L78" s="7" t="n">
-        <f aca="false">ROUND(J78*K78,2)</f>
+      <c r="K78" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L78" s="7">
+        <f t="shared" si="4"/>
         <v>44422</v>
       </c>
-      <c r="M78" s="8" t="n">
-        <f aca="false">ROUND(J78+L78,2)</f>
+      <c r="M78" s="8">
+        <f t="shared" si="5"/>
         <v>278222</v>
       </c>
       <c r="N78" s="3" t="s">
@@ -7039,7 +6949,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>36</v>
       </c>
@@ -7067,18 +6977,18 @@
       <c r="I79" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="J79" s="5" t="n">
+      <c r="J79" s="5">
         <v>39704</v>
       </c>
-      <c r="K79" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L79" s="7" t="n">
-        <f aca="false">ROUND(J79*K79,2)</f>
+      <c r="K79" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L79" s="7">
+        <f t="shared" si="4"/>
         <v>7543.76</v>
       </c>
-      <c r="M79" s="8" t="n">
-        <f aca="false">ROUND(J79+L79,2)</f>
+      <c r="M79" s="8">
+        <f t="shared" si="5"/>
         <v>47247.76</v>
       </c>
       <c r="N79" s="3" t="s">
@@ -7088,7 +6998,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>36</v>
       </c>
@@ -7116,18 +7026,18 @@
       <c r="I80" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="J80" s="5" t="n">
+      <c r="J80" s="5">
         <v>83640</v>
       </c>
-      <c r="K80" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L80" s="7" t="n">
-        <f aca="false">ROUND(J80*K80,2)</f>
+      <c r="K80" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L80" s="7">
+        <f t="shared" si="4"/>
         <v>15891.6</v>
       </c>
-      <c r="M80" s="8" t="n">
-        <f aca="false">ROUND(J80+L80,2)</f>
+      <c r="M80" s="8">
+        <f t="shared" si="5"/>
         <v>99531.6</v>
       </c>
       <c r="N80" s="3" t="s">
@@ -7137,7 +7047,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>36</v>
       </c>
@@ -7165,19 +7075,19 @@
       <c r="I81" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="J81" s="5" t="n">
+      <c r="J81" s="5">
         <v>31960</v>
       </c>
-      <c r="K81" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L81" s="7" t="n">
-        <f aca="false">ROUND(J81*K81,2)</f>
+      <c r="K81" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L81" s="7">
+        <f t="shared" si="4"/>
         <v>6072.4</v>
       </c>
-      <c r="M81" s="8" t="n">
-        <f aca="false">ROUND(J81+L81,2)</f>
-        <v>38032.4</v>
+      <c r="M81" s="8">
+        <f t="shared" si="5"/>
+        <v>38032.400000000001</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>722</v>
@@ -7186,7 +7096,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>15</v>
       </c>
@@ -7214,18 +7124,18 @@
       <c r="I82" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="J82" s="5" t="n">
+      <c r="J82" s="5">
         <v>15908.8</v>
       </c>
-      <c r="K82" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L82" s="7" t="n">
-        <f aca="false">ROUND(J82*K82,2)</f>
+      <c r="K82" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L82" s="7">
+        <f t="shared" si="4"/>
         <v>3022.67</v>
       </c>
-      <c r="M82" s="8" t="n">
-        <f aca="false">ROUND(J82+L82,2)</f>
+      <c r="M82" s="8">
+        <f t="shared" si="5"/>
         <v>18931.47</v>
       </c>
       <c r="N82" s="3" t="s">
@@ -7235,7 +7145,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>36</v>
       </c>
@@ -7263,18 +7173,18 @@
       <c r="I83" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="J83" s="5" t="n">
+      <c r="J83" s="5">
         <v>185600</v>
       </c>
-      <c r="K83" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L83" s="7" t="n">
-        <f aca="false">ROUND(J83*K83,2)</f>
+      <c r="K83" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L83" s="7">
+        <f t="shared" si="4"/>
         <v>35264</v>
       </c>
-      <c r="M83" s="8" t="n">
-        <f aca="false">ROUND(J83+L83,2)</f>
+      <c r="M83" s="8">
+        <f t="shared" si="5"/>
         <v>220864</v>
       </c>
       <c r="N83" s="3" t="s">
@@ -7284,7 +7194,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>68</v>
       </c>
@@ -7312,18 +7222,18 @@
       <c r="I84" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="J84" s="5" t="n">
+      <c r="J84" s="5">
         <v>61700</v>
       </c>
-      <c r="K84" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L84" s="7" t="n">
-        <f aca="false">ROUND(J84*K84,2)</f>
+      <c r="K84" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L84" s="7">
+        <f t="shared" si="4"/>
         <v>11723</v>
       </c>
-      <c r="M84" s="8" t="n">
-        <f aca="false">ROUND(J84+L84,2)</f>
+      <c r="M84" s="8">
+        <f t="shared" si="5"/>
         <v>73423</v>
       </c>
       <c r="N84" s="3" t="s">
@@ -7333,7 +7243,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>15</v>
       </c>
@@ -7361,19 +7271,19 @@
       <c r="I85" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="J85" s="5" t="n">
+      <c r="J85" s="5">
         <v>169920</v>
       </c>
-      <c r="K85" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L85" s="7" t="n">
-        <f aca="false">ROUND(J85*K85,2)</f>
-        <v>32284.8</v>
-      </c>
-      <c r="M85" s="8" t="n">
-        <f aca="false">ROUND(J85+L85,2)</f>
-        <v>202204.8</v>
+      <c r="K85" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L85" s="7">
+        <f t="shared" si="4"/>
+        <v>32284.799999999999</v>
+      </c>
+      <c r="M85" s="8">
+        <f t="shared" si="5"/>
+        <v>202204.79999999999</v>
       </c>
       <c r="N85" s="3" t="s">
         <v>334</v>
@@ -7382,7 +7292,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>15</v>
       </c>
@@ -7410,19 +7320,19 @@
       <c r="I86" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="J86" s="5" t="n">
+      <c r="J86" s="5">
         <v>15019.2</v>
       </c>
-      <c r="K86" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L86" s="7" t="n">
-        <f aca="false">ROUND(J86*K86,2)</f>
+      <c r="K86" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L86" s="7">
+        <f t="shared" si="4"/>
         <v>2853.65</v>
       </c>
-      <c r="M86" s="8" t="n">
-        <f aca="false">ROUND(J86+L86,2)</f>
-        <v>17872.85</v>
+      <c r="M86" s="8">
+        <f t="shared" si="5"/>
+        <v>17872.849999999999</v>
       </c>
       <c r="N86" s="3" t="s">
         <v>761</v>
@@ -7431,7 +7341,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>88</v>
       </c>
@@ -7459,19 +7369,19 @@
       <c r="I87" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="J87" s="5" t="n">
+      <c r="J87" s="5">
         <v>62040</v>
       </c>
-      <c r="K87" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L87" s="7" t="n">
-        <f aca="false">ROUND(J87*K87,2)</f>
+      <c r="K87" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L87" s="7">
+        <f t="shared" si="4"/>
         <v>11787.6</v>
       </c>
-      <c r="M87" s="8" t="n">
-        <f aca="false">ROUND(J87+L87,2)</f>
-        <v>73827.6</v>
+      <c r="M87" s="8">
+        <f t="shared" si="5"/>
+        <v>73827.600000000006</v>
       </c>
       <c r="N87" s="3" t="s">
         <v>157</v>
@@ -7480,7 +7390,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>68</v>
       </c>
@@ -7508,19 +7418,19 @@
       <c r="I88" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="J88" s="5" t="n">
+      <c r="J88" s="5">
         <v>46192</v>
       </c>
-      <c r="K88" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L88" s="7" t="n">
-        <f aca="false">ROUND(J88*K88,2)</f>
+      <c r="K88" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L88" s="7">
+        <f t="shared" si="4"/>
         <v>8776.48</v>
       </c>
-      <c r="M88" s="8" t="n">
-        <f aca="false">ROUND(J88+L88,2)</f>
-        <v>54968.48</v>
+      <c r="M88" s="8">
+        <f t="shared" si="5"/>
+        <v>54968.480000000003</v>
       </c>
       <c r="N88" s="3" t="s">
         <v>778</v>
@@ -7529,7 +7439,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>47</v>
       </c>
@@ -7557,19 +7467,19 @@
       <c r="I89" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="J89" s="5" t="n">
+      <c r="J89" s="5">
         <v>46224</v>
       </c>
-      <c r="K89" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L89" s="7" t="n">
-        <f aca="false">ROUND(J89*K89,2)</f>
+      <c r="K89" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L89" s="7">
+        <f t="shared" si="4"/>
         <v>8782.56</v>
       </c>
-      <c r="M89" s="8" t="n">
-        <f aca="false">ROUND(J89+L89,2)</f>
-        <v>55006.56</v>
+      <c r="M89" s="8">
+        <f t="shared" si="5"/>
+        <v>55006.559999999998</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>787</v>
@@ -7578,7 +7488,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>47</v>
       </c>
@@ -7606,19 +7516,19 @@
       <c r="I90" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="J90" s="5" t="n">
+      <c r="J90" s="5">
         <v>25960</v>
       </c>
-      <c r="K90" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L90" s="7" t="n">
-        <f aca="false">ROUND(J90*K90,2)</f>
-        <v>4932.4</v>
-      </c>
-      <c r="M90" s="8" t="n">
-        <f aca="false">ROUND(J90+L90,2)</f>
-        <v>30892.4</v>
+      <c r="K90" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L90" s="7">
+        <f t="shared" si="4"/>
+        <v>4932.3999999999996</v>
+      </c>
+      <c r="M90" s="8">
+        <f t="shared" si="5"/>
+        <v>30892.400000000001</v>
       </c>
       <c r="N90" s="3" t="s">
         <v>795</v>
@@ -7627,7 +7537,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>172</v>
       </c>
@@ -7655,18 +7565,18 @@
       <c r="I91" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="J91" s="5" t="n">
+      <c r="J91" s="5">
         <v>39872</v>
       </c>
-      <c r="K91" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L91" s="7" t="n">
-        <f aca="false">ROUND(J91*K91,2)</f>
+      <c r="K91" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L91" s="7">
+        <f t="shared" si="4"/>
         <v>7575.68</v>
       </c>
-      <c r="M91" s="8" t="n">
-        <f aca="false">ROUND(J91+L91,2)</f>
+      <c r="M91" s="8">
+        <f t="shared" si="5"/>
         <v>47447.68</v>
       </c>
       <c r="N91" s="3" t="s">
@@ -7676,7 +7586,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>15</v>
       </c>
@@ -7704,18 +7614,18 @@
       <c r="I92" s="4" t="s">
         <v>809</v>
       </c>
-      <c r="J92" s="5" t="n">
+      <c r="J92" s="5">
         <v>10388</v>
       </c>
-      <c r="K92" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L92" s="7" t="n">
-        <f aca="false">ROUND(J92*K92,2)</f>
+      <c r="K92" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L92" s="7">
+        <f t="shared" si="4"/>
         <v>1973.72</v>
       </c>
-      <c r="M92" s="8" t="n">
-        <f aca="false">ROUND(J92+L92,2)</f>
+      <c r="M92" s="8">
+        <f t="shared" si="5"/>
         <v>12361.72</v>
       </c>
       <c r="N92" s="3" t="s">
@@ -7725,7 +7635,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>57</v>
       </c>
@@ -7753,18 +7663,18 @@
       <c r="I93" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="J93" s="5" t="n">
+      <c r="J93" s="5">
         <v>5880</v>
       </c>
-      <c r="K93" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L93" s="7" t="n">
-        <f aca="false">ROUND(J93*K93,2)</f>
+      <c r="K93" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L93" s="7">
+        <f t="shared" si="4"/>
         <v>1117.2</v>
       </c>
-      <c r="M93" s="8" t="n">
-        <f aca="false">ROUND(J93+L93,2)</f>
+      <c r="M93" s="8">
+        <f t="shared" si="5"/>
         <v>6997.2</v>
       </c>
       <c r="N93" s="3" t="s">
@@ -7774,7 +7684,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>15</v>
       </c>
@@ -7802,18 +7712,18 @@
       <c r="I94" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="J94" s="5" t="n">
+      <c r="J94" s="5">
         <v>17544</v>
       </c>
-      <c r="K94" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L94" s="7" t="n">
-        <f aca="false">ROUND(J94*K94,2)</f>
+      <c r="K94" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L94" s="7">
+        <f t="shared" si="4"/>
         <v>3333.36</v>
       </c>
-      <c r="M94" s="8" t="n">
-        <f aca="false">ROUND(J94+L94,2)</f>
+      <c r="M94" s="8">
+        <f t="shared" si="5"/>
         <v>20877.36</v>
       </c>
       <c r="N94" s="3" t="s">
@@ -7823,7 +7733,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>15</v>
       </c>
@@ -7851,18 +7761,18 @@
       <c r="I95" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="J95" s="5" t="n">
+      <c r="J95" s="5">
         <v>37251</v>
       </c>
-      <c r="K95" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L95" s="7" t="n">
-        <f aca="false">ROUND(J95*K95,2)</f>
+      <c r="K95" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L95" s="7">
+        <f t="shared" si="4"/>
         <v>7077.69</v>
       </c>
-      <c r="M95" s="8" t="n">
-        <f aca="false">ROUND(J95+L95,2)</f>
+      <c r="M95" s="8">
+        <f t="shared" si="5"/>
         <v>44328.69</v>
       </c>
       <c r="N95" s="3" t="s">
@@ -7872,7 +7782,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>88</v>
       </c>
@@ -7900,18 +7810,18 @@
       <c r="I96" s="4" t="s">
         <v>836</v>
       </c>
-      <c r="J96" s="5" t="n">
+      <c r="J96" s="5">
         <v>20772</v>
       </c>
-      <c r="K96" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L96" s="7" t="n">
-        <f aca="false">ROUND(J96*K96,2)</f>
+      <c r="K96" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L96" s="7">
+        <f t="shared" si="4"/>
         <v>3946.68</v>
       </c>
-      <c r="M96" s="8" t="n">
-        <f aca="false">ROUND(J96+L96,2)</f>
+      <c r="M96" s="8">
+        <f t="shared" si="5"/>
         <v>24718.68</v>
       </c>
       <c r="N96" s="3" t="s">
@@ -7921,7 +7831,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>57</v>
       </c>
@@ -7949,19 +7859,19 @@
       <c r="I97" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="J97" s="5" t="n">
+      <c r="J97" s="5">
         <v>28048</v>
       </c>
-      <c r="K97" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L97" s="7" t="n">
-        <f aca="false">ROUND(J97*K97,2)</f>
+      <c r="K97" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L97" s="7">
+        <f t="shared" si="4"/>
         <v>5329.12</v>
       </c>
-      <c r="M97" s="8" t="n">
-        <f aca="false">ROUND(J97+L97,2)</f>
-        <v>33377.12</v>
+      <c r="M97" s="8">
+        <f t="shared" si="5"/>
+        <v>33377.120000000003</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>207</v>
@@ -7970,7 +7880,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>47</v>
       </c>
@@ -7998,18 +7908,18 @@
       <c r="I98" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="J98" s="5" t="n">
+      <c r="J98" s="5">
         <v>30052</v>
       </c>
-      <c r="K98" s="6" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="L98" s="7" t="n">
-        <f aca="false">ROUND(J98*K98,2)</f>
+      <c r="K98" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L98" s="7">
+        <f t="shared" ref="L98:L129" si="6">ROUND(J98*K98,2)</f>
         <v>2103.64</v>
       </c>
-      <c r="M98" s="8" t="n">
-        <f aca="false">ROUND(J98+L98,2)</f>
+      <c r="M98" s="8">
+        <f t="shared" ref="M98:M129" si="7">ROUND(J98+L98,2)</f>
         <v>32155.64</v>
       </c>
       <c r="N98" s="3" t="s">
@@ -8019,7 +7929,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>15</v>
       </c>
@@ -8047,18 +7957,18 @@
       <c r="I99" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="J99" s="5" t="n">
+      <c r="J99" s="5">
         <v>99600</v>
       </c>
-      <c r="K99" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L99" s="7" t="n">
-        <f aca="false">ROUND(J99*K99,2)</f>
+      <c r="K99" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L99" s="7">
+        <f t="shared" si="6"/>
         <v>18924</v>
       </c>
-      <c r="M99" s="8" t="n">
-        <f aca="false">ROUND(J99+L99,2)</f>
+      <c r="M99" s="8">
+        <f t="shared" si="7"/>
         <v>118524</v>
       </c>
       <c r="N99" s="3" t="s">
@@ -8068,7 +7978,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>172</v>
       </c>
@@ -8096,18 +8006,18 @@
       <c r="I100" s="4" t="s">
         <v>861</v>
       </c>
-      <c r="J100" s="5" t="n">
+      <c r="J100" s="5">
         <v>56920</v>
       </c>
-      <c r="K100" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L100" s="7" t="n">
-        <f aca="false">ROUND(J100*K100,2)</f>
+      <c r="K100" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L100" s="7">
+        <f t="shared" si="6"/>
         <v>10814.8</v>
       </c>
-      <c r="M100" s="8" t="n">
-        <f aca="false">ROUND(J100+L100,2)</f>
+      <c r="M100" s="8">
+        <f t="shared" si="7"/>
         <v>67734.8</v>
       </c>
       <c r="N100" s="3" t="s">
@@ -8117,7 +8027,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>88</v>
       </c>
@@ -8145,18 +8055,18 @@
       <c r="I101" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="J101" s="5" t="n">
+      <c r="J101" s="5">
         <v>73266</v>
       </c>
-      <c r="K101" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="L101" s="7" t="n">
-        <f aca="false">ROUND(J101*K101,2)</f>
+      <c r="K101" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="L101" s="7">
+        <f t="shared" si="6"/>
         <v>13920.54</v>
       </c>
-      <c r="M101" s="8" t="n">
-        <f aca="false">ROUND(J101+L101,2)</f>
+      <c r="M101" s="8">
+        <f t="shared" si="7"/>
         <v>87186.54</v>
       </c>
       <c r="N101" s="3" t="s">
@@ -8166,53 +8076,53 @@
         <v>869</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I102" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="J102" s="10" t="n">
-        <f aca="false">SUM(J2:J101)</f>
-        <v>4006480.95</v>
-      </c>
-      <c r="L102" s="10" t="n">
-        <f aca="false">SUM(L2:L101)</f>
-        <v>755696.51</v>
-      </c>
-      <c r="M102" s="10" t="n">
-        <f aca="false">SUM(M2:M101)</f>
-        <v>4762177.46</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J102" s="10">
+        <f>SUM(J2:J101)</f>
+        <v>4016480.95</v>
+      </c>
+      <c r="L102" s="10">
+        <f>SUM(L2:L101)</f>
+        <v>757596.51000000024</v>
+      </c>
+      <c r="M102" s="10">
+        <f>SUM(M2:M101)</f>
+        <v>4774077.46</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
         <v>874</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O101"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:O101" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b0078d80-d8fa-41c0-a03d-2fc8bfbf8ef3}" enabled="1" method="Standard" siteId="{1a5fb97d-e8d3-49e2-b059-92746ee77d81}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Referenztabelle_Rechnungen.xlsx
+++ b/Referenztabelle_Rechnungen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fgroup-my.sharepoint.com/personal/leonard_verclas_freudenberg_com/Documents/02_Studium_DHBW/PA 2/Projektarbeit_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_1373589E6EA26D9A1A97E98B862CC5E341F0CACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{197868DF-8A72-4890-813F-A7FED2AE9AAB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C236E29A148D72B1158823B4D6A8493DBF6A7C8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2250" yWindow="1920" windowWidth="21600" windowHeight="12525" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rechnungsuebersicht" sheetId="1" r:id="rId1"/>
@@ -2932,6 +2932,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3305,18 +3309,18 @@
         <v>44</v>
       </c>
       <c r="J4" s="5">
-        <v>36930</v>
+        <v>26930</v>
       </c>
       <c r="K4" s="6">
         <v>0.19</v>
       </c>
       <c r="L4" s="7">
         <f t="shared" si="0"/>
-        <v>7016.7</v>
+        <v>5116.7</v>
       </c>
       <c r="M4" s="8">
-        <f>ROUND(J4+L4,2)</f>
-        <v>43946.7</v>
+        <f t="shared" si="1"/>
+        <v>32046.7</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>45</v>
@@ -8082,15 +8086,15 @@
       </c>
       <c r="J102" s="10">
         <f>SUM(J2:J101)</f>
-        <v>4016480.95</v>
+        <v>4006480.95</v>
       </c>
       <c r="L102" s="10">
         <f>SUM(L2:L101)</f>
-        <v>757596.51000000024</v>
+        <v>755696.51000000024</v>
       </c>
       <c r="M102" s="10">
         <f>SUM(M2:M101)</f>
-        <v>4774077.46</v>
+        <v>4762177.46</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
@@ -8123,6 +8127,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{b0078d80-d8fa-41c0-a03d-2fc8bfbf8ef3}" enabled="1" method="Standard" siteId="{1a5fb97d-e8d3-49e2-b059-92746ee77d81}" contentBits="0" removed="0"/>
+  <clbl:label id="{b0078d80-d8fa-41c0-a03d-2fc8bfbf8ef3}" enabled="1" method="Standard" siteId="{1a5fb97d-e8d3-49e2-b059-92746ee77d81}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/Referenztabelle_Rechnungen.xlsx
+++ b/Referenztabelle_Rechnungen.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_C236E29A148D72B1158823B4D6A8493DBF6A7C8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2250" yWindow="1920" windowWidth="21600" windowHeight="12525" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rechnungsuebersicht" sheetId="1" r:id="rId1"/>
@@ -2932,10 +2932,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7919,11 +7915,11 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="L98" s="7">
-        <f t="shared" ref="L98:L129" si="6">ROUND(J98*K98,2)</f>
+        <f t="shared" ref="L98:L101" si="6">ROUND(J98*K98,2)</f>
         <v>2103.64</v>
       </c>
       <c r="M98" s="8">
-        <f t="shared" ref="M98:M129" si="7">ROUND(J98+L98,2)</f>
+        <f t="shared" ref="M98:M101" si="7">ROUND(J98+L98,2)</f>
         <v>32155.64</v>
       </c>
       <c r="N98" s="3" t="s">
